--- a/OWSA_Illustrative_Model.xlsx
+++ b/OWSA_Illustrative_Model.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dylann/Desktop/Workspace/DSA-Whatif/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A30013-AE76-914C-8E18-9ED753EFCD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A576BCA1-2DF1-244D-9C99-467E7B90C749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{A60188B9-612A-604A-B0A4-8D28EDA36197}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="21460" activeTab="1" xr2:uid="{A60188B9-612A-604A-B0A4-8D28EDA36197}"/>
   </bookViews>
   <sheets>
     <sheet name="DSA_What-If" sheetId="3" r:id="rId1"/>
-    <sheet name="Blank Sheet" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="DSA_DAF" sheetId="5" r:id="rId2"/>
+    <sheet name="Blank Sheet" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="HCed">'DSA_What-If'!$M$23</definedName>
@@ -33,6 +34,7 @@
     <definedName name="RPedLE">'DSA_What-If'!$M$30</definedName>
     <definedName name="RPldC">'DSA_What-If'!$M$25</definedName>
     <definedName name="RPldLE">'DSA_What-If'!$M$31</definedName>
+    <definedName name="Tree">_xlfn.LAMBDA(_xlpm.p,     _xlfn.LET(         _xlpm.RPed,INDEX(_xlpm.p,1),         _xlpm.PCed,INDEX(_xlpm.p,2),         _xlpm.HCed,INDEX(_xlpm.p,3),         _xlpm.RPedC,INDEX(_xlpm.p,4),         _xlpm.RPldC,INDEX(_xlpm.p,5),         _xlpm.PCedC,INDEX(_xlpm.p,6),         _xlpm.PCldC,INDEX(_xlpm.p,7),         _xlpm.HCedC,INDEX(_xlpm.p,8),         _xlpm.HCldC,INDEX(_xlpm.p,9),         _xlpm.RPedLE,INDEX(_xlpm.p,10),         _xlpm.RPldLE,INDEX(_xlpm.p,11),         _xlpm.PCedLE,INDEX(_xlpm.p,12),         _xlpm.PCldLE,INDEX(_xlpm.p,13),         _xlpm.HCedLE,INDEX(_xlpm.p,14),         _xlpm.HCldLE,INDEX(_xlpm.p,15),          _xlpm.rpCost,_xlpm.RPed*_xlpm.RPedC+(1-_xlpm.RPed)*_xlpm.RPldC,         _xlpm.pcCost,_xlpm.PCed*_xlpm.PCedC+(1-_xlpm.PCed)*_xlpm.PCldC,         _xlpm.hcCost,_xlpm.HCed*_xlpm.HCedC+(1-_xlpm.HCed)*_xlpm.HCldC,          _xlpm.rpEffect,_xlpm.RPed*_xlpm.RPedLE+(1-_xlpm.RPed)*_xlpm.RPldLE,         _xlpm.pcEffect,_xlpm.PCed*_xlpm.PCedLE+(1-_xlpm.PCed)*_xlpm.PCldLE,         _xlpm.hcEffect,_xlpm.HCed*_xlpm.HCedLE+(1-_xlpm.HCed)*_xlpm.HCldLE,          _xlpm.dcPC,_xlpm.pcCost-_xlpm.rpCost,         _xlpm.dcHC,_xlpm.hcCost-_xlpm.pcCost,         _xlpm.dePC,_xlpm.pcEffect-_xlpm.rpEffect,         _xlpm.deHC,_xlpm.hcEffect-_xlpm.pcEffect,          _xlpm.icerPC,IFERROR(_xlpm.dcPC/_xlpm.dePC,NA()),         _xlpm.icerHC,IFERROR(_xlpm.dcHC/_xlpm.deHC,NA()),          _xlpm.inmbPC,_xlpm.dePC*DSA_DAF!$W$28-_xlpm.dcPC,         _xlpm.inmbHC,_xlpm.deHC*DSA_DAF!$W$28-_xlpm.dcHC,          _xlfn.VSTACK(             _xlfn.HSTACK(_xlpm.rpCost,_xlpm.rpEffect,0,0,0,0),             _xlfn.HSTACK(_xlpm.pcCost,_xlpm.pcEffect,_xlpm.dcPC,_xlpm.dePC,_xlpm.icerPC,_xlpm.inmbPC),             _xlfn.HSTACK(_xlpm.hcCost,_xlpm.hcEffect,_xlpm.dcHC,_xlpm.deHC,_xlpm.icerHC,_xlpm.inmbHC)         )     ) )</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -123,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="98">
   <si>
     <t>BLANK SHEET TEMPLATE</t>
   </si>
@@ -461,6 +463,15 @@
   <si>
     <t>Source: Gray AM, Clarke PM, Wolstenholme JL, Wordsworth S. Applied Methods of Cost-effectiveness Analysis in Health Care. Oxford: Oxford University Press; 2011.</t>
   </si>
+  <si>
+    <t>Deterministic Sensitivity Analysis (DSA) | Dynamic Array Function</t>
+  </si>
+  <si>
+    <t>Enter the function in AP8:</t>
+  </si>
+  <si>
+    <t>4. In a Single-cell</t>
+  </si>
 </sst>
 </file>
 
@@ -474,7 +485,7 @@
     <numFmt numFmtId="167" formatCode="&quot;£&quot;#,##0.00"/>
     <numFmt numFmtId="168" formatCode="&quot;£&quot;#,##0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -593,6 +604,33 @@
       <i/>
       <sz val="8"/>
       <color theme="1" tint="0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFF5F8F9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF077F82"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1179,7 +1217,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1535,9 +1573,6 @@
     <xf numFmtId="167" fontId="5" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1601,6 +1636,87 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="12" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="12" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="12" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="12" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1652,32 +1768,11 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1688,8 +1783,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF077F82"/>
       <color rgb="FFF5F8F9"/>
-      <color rgb="FF077F82"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3276,6 +3371,1579 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.45929537216973421"/>
+          <c:y val="5.8312644910549563E-2"/>
+          <c:w val="0.50323695564778459"/>
+          <c:h val="0.79537473905028233"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DSA_DAF!$AJ$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>INMB - LL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>DSA_DAF!$AF$10:$AF$19</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Life expectancy of early detection in primary care (6.3, 7.7)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Life expectancy of early detection in routine practice (6.3, 7.7)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Probability of early detection in primary care (0.36, 0.44)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Probability of early detection in routine practice (0.315, 0.385)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Life expectancy of late detection in routine practice (1.35, 1.65)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Life expectancy of late detection in primary care (1.35, 1.65)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cost of late detection in routine practice (10,818., 13,222.)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Cost of late detection in primary care (11,520., 14,080.)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Cost of early detection in primary care (3,510., 4,290.)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Cost of early detection in routine practice (2,727., 3,333.)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DSA_DAF!$AJ$10:$AJ$19</c:f>
+              <c:numCache>
+                <c:formatCode>"£"#,##0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-466.49999999999784</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10033.500000000009</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>377.50000000001205</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9298.1500000000069</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7083.50000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3333.50000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4352.2000000000071</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5901.5000000000073</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5289.5000000000073</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5027.450000000008</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0C6D-5C46-AFBC-610AE7FF82DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DSA_DAF!$AK$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>INMB - UL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>DSA_DAF!$AF$10:$AF$19</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Life expectancy of early detection in primary care (6.3, 7.7)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Life expectancy of early detection in routine practice (6.3, 7.7)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Probability of early detection in primary care (0.36, 0.44)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Probability of early detection in routine practice (0.315, 0.385)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Life expectancy of late detection in routine practice (1.35, 1.65)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Life expectancy of late detection in primary care (1.35, 1.65)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cost of late detection in routine practice (10,818., 13,222.)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Cost of late detection in primary care (11,520., 14,080.)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Cost of early detection in primary care (3,510., 4,290.)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Cost of early detection in routine practice (2,727., 3,333.)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DSA_DAF!$AK$10:$AK$19</c:f>
+              <c:numCache>
+                <c:formatCode>"£"#,##0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>10733.500000000013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>233.49999999999613</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9889.5000000000109</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>968.85000000000082</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3183.5000000000041</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6933.5000000000045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5914.8000000000084</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4365.5000000000073</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4977.5000000000073</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5239.5500000000065</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0C6D-5C46-AFBC-610AE7FF82DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="60"/>
+        <c:overlap val="100"/>
+        <c:axId val="1607709008"/>
+        <c:axId val="1607710736"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1607709008"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1607710736"/>
+        <c:crossesAt val="5133.5"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="300"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1607710736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="11000"/>
+          <c:min val="-500"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1"/>
+                  <a:t>Incremental</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="zh-CN" sz="1000" b="1"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1"/>
+                  <a:t>Net</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="zh-CN" sz="1000" b="1"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1"/>
+                  <a:t>Monetary</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="zh-CN" sz="1000" b="1"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1"/>
+                  <a:t>Benefit</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.56837091015796937"/>
+              <c:y val="0.92287467191601047"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="&quot;£&quot;#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="high"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1607709008"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="2000"/>
+        <c:minorUnit val="500"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900" b="0" i="0">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.45845377450656277"/>
+          <c:y val="5.8312644910549563E-2"/>
+          <c:w val="0.50407855827559545"/>
+          <c:h val="0.79537473905028233"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DSA_DAF!$AJ$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>INMB - LL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>DSA_DAF!$AF$36:$AF$45</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Life expectancy of early detection in hospital care (6.3, 7.7)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Life expectancy of early detection in primary care (6.3, 7.7)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Probability of early detection in hospital care (0.405, 0.495)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Probability of early detection in primary care (0.36, 0.44)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Life expectancy of late detection in primary care (1.35, 1.65)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Life expectancy of late detection in hospital care (1.35, 1.65)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cost of late detection in hospital care (12,960., 15,840.)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Cost of late detection in primary care (11,520., 14,080.)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Cost of early detection in hospital care (5,580., 6,820.)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Cost of early detection in primary care (3,510., 4,290.)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DSA_DAF!$AJ$36:$AJ$45</c:f>
+              <c:numCache>
+                <c:formatCode>"£"#,##0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-2270.0000000000009</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9630.0000000000036</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1289.0000000000027</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8785.9999999999927</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5829.9999999999955</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2379.9999999999977</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4821.9999999999982</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3261.9999999999982</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4308.9999999999982</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3873.9999999999982</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E534-F442-8584-E441D61F6C04}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DSA_DAF!$AK$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>INMB - UL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>DSA_DAF!$AF$36:$AF$45</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Life expectancy of early detection in hospital care (6.3, 7.7)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Life expectancy of early detection in primary care (6.3, 7.7)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Probability of early detection in hospital care (0.405, 0.495)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Probability of early detection in primary care (0.36, 0.44)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Life expectancy of late detection in primary care (1.35, 1.65)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Life expectancy of late detection in hospital care (1.35, 1.65)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cost of late detection in hospital care (12,960., 15,840.)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Cost of late detection in primary care (11,520., 14,080.)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Cost of early detection in hospital care (5,580., 6,820.)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Cost of early detection in primary care (3,510., 4,290.)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DSA_DAF!$AK$36:$AK$45</c:f>
+              <c:numCache>
+                <c:formatCode>"£"#,##0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>10330.000000000015</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1570.0000000000068</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9349.0000000000018</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-726.00000000000568</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2230.0000000000009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5679.9999999999982</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3237.9999999999964</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4797.9999999999982</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3750.9999999999964</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4185.9999999999982</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E534-F442-8584-E441D61F6C04}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="60"/>
+        <c:overlap val="100"/>
+        <c:axId val="1607709008"/>
+        <c:axId val="1607710736"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1607709008"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1607710736"/>
+        <c:crossesAt val="4030"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="300"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1607710736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="11000"/>
+          <c:min val="-2500"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1"/>
+                  <a:t>Incremental</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="zh-CN" sz="1000" b="1"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1"/>
+                  <a:t>Net</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="zh-CN" sz="1000" b="1"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1"/>
+                  <a:t>Monetary</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="zh-CN" sz="1000" b="1"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1"/>
+                  <a:t>Benefit</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.56837091015796937"/>
+              <c:y val="0.92287467191601047"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="&quot;£&quot;#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="high"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1607709008"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="2000"/>
+        <c:minorUnit val="500"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900" b="0" i="0">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1000" b="1"/>
+              <a:t>Incremental Cost-Effectiveness</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="1"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.15462527229803136"/>
+          <c:y val="0.12669683257918551"/>
+          <c:w val="0.74985843303035471"/>
+          <c:h val="0.76244343891402711"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DSA_DAF!$Q$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Routine Practice</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="10"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>DSA_DAF!$S$31</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.4249999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>DSA_DAF!$R$31</c:f>
+              <c:numCache>
+                <c:formatCode>"£"#,##0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8873.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B562-0240-8574-16B786C8EA38}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DSA_DAF!$Q$32</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Primary Care</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="10"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>DSA_DAF!$S$32</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>DSA_DAF!$R$32</c:f>
+              <c:numCache>
+                <c:formatCode>"£"#,##0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>9240</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B562-0240-8574-16B786C8EA38}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DSA_DAF!$Q$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hospital Care</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="10"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>DSA_DAF!$S$33</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.9750000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>DSA_DAF!$R$33</c:f>
+              <c:numCache>
+                <c:formatCode>"£"#,##0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10710</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B562-0240-8574-16B786C8EA38}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="401351871"/>
+        <c:axId val="1"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>CE Frontier</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B562-0240-8574-16B786C8EA38}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:xVal>
+            <c:numRef>
+              <c:f>DSA_DAF!$S$31:$S$33</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>3.4249999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.9750000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>DSA_DAF!$R$31:$R$33</c:f>
+              <c:numCache>
+                <c:formatCode>"£"#,##0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>8873.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9240</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10710</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-B562-0240-8574-16B786C8EA38}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="401351871"/>
+        <c:axId val="1"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="401351871"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="3.4"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="3175">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="8000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="&quot;£&quot;#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="3175">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="401351871"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.70559583029603934"/>
+          <c:y val="0.36235364190039943"/>
+          <c:w val="0.29440416970396055"/>
+          <c:h val="0.35302966135553671"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="3175">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </c:spPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="Helvetica" pitchFamily="2" charset="0"/>
+          <a:ea typeface="Arial"/>
+          <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3317,6 +4985,86 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3862,6 +5610,1016 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5141,6 +7899,781 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1010385</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>134718</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>110096</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>107546</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9DB7D0B-8D11-9C44-8973-7A733593F32C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15031185" y="4300318"/>
+          <a:ext cx="230011" cy="226828"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1024419</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>140331</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>123351</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>116335</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Oval 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE316EE1-83BA-4744-851D-A2071CD2AA9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16175519" y="2527931"/>
+          <a:ext cx="229232" cy="230004"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1029471</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>138366</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>128403</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114370</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Oval 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5EC79D1-6AAE-D44A-8316-ED160F1EB88C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16180571" y="4303966"/>
+          <a:ext cx="229232" cy="230004"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1027506</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>136402</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>126438</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>112405</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Oval 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EA31CE6-0461-C141-8C98-9214FBE3A4CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16178606" y="6181602"/>
+          <a:ext cx="229232" cy="230003"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>989338</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>133315</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>88270</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>111767</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Triangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A879C593-8363-2B4B-91BA-04ABF0A20F01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="18399428" y="2014525"/>
+          <a:ext cx="232452" cy="229232"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>987374</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>140421</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>86306</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>118873</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Triangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{744AA62D-87D1-3E47-9F6C-0188A8038D9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="18397464" y="3037631"/>
+          <a:ext cx="232452" cy="229232"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>992427</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>136402</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>91359</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>114854</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Triangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91967343-44A1-4243-A19D-8C3FBDEB1DB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="18402517" y="3795612"/>
+          <a:ext cx="232452" cy="229232"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>990463</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>134437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>89395</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>112890</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Triangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C95D121D-9D02-044B-9D73-6F51D9DD0818}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="18400552" y="4911248"/>
+          <a:ext cx="232453" cy="229232"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>994390</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>140420</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>93322</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>118873</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Triangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{764C3F63-8B63-684F-BE21-18462EAB00AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="18404479" y="5679231"/>
+          <a:ext cx="232453" cy="229232"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>992426</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>138456</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>91358</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>116908</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Triangle 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C4BF085-2682-4E44-BB55-3AFE1F8507FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="18402516" y="6693266"/>
+          <a:ext cx="232452" cy="229232"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Tornado Diagram">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6545FF66-EAB5-2D46-AE6D-830BCAD9D276}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="13" name="Tornado Diagram">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CAC00C7-741D-C040-88E0-68202DED8795}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="19655327" y="2764101"/>
+    <xdr:ext cx="5155596" cy="2933095"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="17" name="CEF">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45ED8946-AD39-C5AA-BD06-77D6D02443FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5470,7 +9003,7 @@
     <col min="10" max="10" width="10.83203125" style="12" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" style="12" customWidth="1"/>
     <col min="12" max="13" width="13.33203125" style="12" customWidth="1"/>
-    <col min="14" max="14" width="2.6640625" style="12" customWidth="1"/>
+    <col min="14" max="14" width="2.83203125" style="12" customWidth="1"/>
     <col min="15" max="15" width="6.83203125" style="12" customWidth="1"/>
     <col min="16" max="16" width="2.83203125" style="12" customWidth="1"/>
     <col min="17" max="17" width="13" style="12" customWidth="1"/>
@@ -5479,7 +9012,7 @@
     <col min="25" max="25" width="14.83203125" style="12"/>
     <col min="26" max="26" width="4.6640625" style="12" customWidth="1"/>
     <col min="27" max="28" width="14.83203125" style="12"/>
-    <col min="29" max="29" width="2.6640625" style="12" customWidth="1"/>
+    <col min="29" max="29" width="2.83203125" style="12" customWidth="1"/>
     <col min="30" max="30" width="6.83203125" style="12" customWidth="1"/>
     <col min="31" max="31" width="2.83203125" style="12" customWidth="1"/>
     <col min="32" max="32" width="13.5" style="64" customWidth="1"/>
@@ -5489,25 +9022,25 @@
     <col min="41" max="41" width="6.6640625" style="64" customWidth="1"/>
     <col min="42" max="42" width="47.6640625" style="64" customWidth="1"/>
     <col min="43" max="48" width="12.83203125" style="64" customWidth="1"/>
-    <col min="49" max="49" width="2.6640625" style="12" customWidth="1"/>
+    <col min="49" max="49" width="2.83203125" style="12" customWidth="1"/>
     <col min="50" max="16384" width="14.83203125" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:49" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="145" t="s">
+      <c r="C1" s="171" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
       <c r="P1" s="26"/>
       <c r="Q1" s="26"/>
       <c r="R1" s="26"/>
@@ -5543,18 +9076,18 @@
       <c r="AW1" s="26"/>
     </row>
     <row r="2" spans="3:49" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="145"/>
-      <c r="L2" s="145"/>
-      <c r="M2" s="145"/>
-      <c r="N2" s="145"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
       <c r="P2" s="26"/>
       <c r="Q2" s="26"/>
       <c r="R2" s="26"/>
@@ -5590,18 +9123,18 @@
       <c r="AW2" s="26"/>
     </row>
     <row r="3" spans="3:49" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="145"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="145"/>
-      <c r="H3" s="145"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="145"/>
-      <c r="K3" s="145"/>
-      <c r="L3" s="145"/>
-      <c r="M3" s="145"/>
-      <c r="N3" s="145"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="171"/>
       <c r="P3" s="26"/>
       <c r="Q3" s="26"/>
       <c r="R3" s="26"/>
@@ -5709,10 +9242,10 @@
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
-      <c r="L6" s="166" t="s">
+      <c r="L6" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="M6" s="166"/>
+      <c r="M6" s="184"/>
       <c r="N6" s="7"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="54" t="s">
@@ -5727,10 +9260,10 @@
       <c r="X6" s="13"/>
       <c r="Y6" s="24"/>
       <c r="Z6" s="24"/>
-      <c r="AA6" s="158" t="s">
+      <c r="AA6" s="166" t="s">
         <v>8</v>
       </c>
-      <c r="AB6" s="158"/>
+      <c r="AB6" s="166"/>
       <c r="AC6" s="7"/>
       <c r="AE6" s="6"/>
       <c r="AF6" s="102" t="s">
@@ -5758,21 +9291,21 @@
     </row>
     <row r="7" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C7" s="6"/>
-      <c r="D7" s="146" t="s">
+      <c r="D7" s="172" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="147"/>
-      <c r="F7" s="147"/>
-      <c r="G7" s="147"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="148"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="166"/>
-      <c r="M7" s="166"/>
+      <c r="E7" s="173"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="173"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="174"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="184"/>
+      <c r="M7" s="184"/>
       <c r="N7" s="7"/>
       <c r="P7" s="6"/>
-      <c r="Q7" s="140" t="s">
+      <c r="Q7" s="139" t="s">
         <v>94</v>
       </c>
       <c r="R7" s="13"/>
@@ -5819,16 +9352,16 @@
     </row>
     <row r="8" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C8" s="6"/>
-      <c r="D8" s="149"/>
-      <c r="E8" s="150"/>
-      <c r="F8" s="150"/>
-      <c r="G8" s="150"/>
-      <c r="H8" s="150"/>
-      <c r="I8" s="150"/>
-      <c r="J8" s="151"/>
-      <c r="K8" s="124"/>
+      <c r="D8" s="175"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="177"/>
+      <c r="K8" s="123"/>
       <c r="L8" s="34"/>
-      <c r="M8" s="121" t="s">
+      <c r="M8" s="120" t="s">
         <v>15</v>
       </c>
       <c r="N8" s="7"/>
@@ -5836,10 +9369,10 @@
       <c r="Q8" s="13"/>
       <c r="R8" s="13"/>
       <c r="S8" s="13"/>
-      <c r="T8" s="144" t="s">
+      <c r="T8" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="U8" s="144"/>
+      <c r="U8" s="170"/>
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
@@ -5888,16 +9421,16 @@
     </row>
     <row r="9" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C9" s="6"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="150"/>
-      <c r="F9" s="150"/>
-      <c r="G9" s="150"/>
-      <c r="H9" s="150"/>
-      <c r="I9" s="150"/>
-      <c r="J9" s="151"/>
-      <c r="K9" s="124"/>
+      <c r="D9" s="175"/>
+      <c r="E9" s="176"/>
+      <c r="F9" s="176"/>
+      <c r="G9" s="176"/>
+      <c r="H9" s="176"/>
+      <c r="I9" s="176"/>
+      <c r="J9" s="177"/>
+      <c r="K9" s="123"/>
       <c r="L9" s="56"/>
-      <c r="M9" s="121" t="s">
+      <c r="M9" s="120" t="s">
         <v>9</v>
       </c>
       <c r="N9" s="7"/>
@@ -5953,16 +9486,16 @@
     </row>
     <row r="10" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C10" s="6"/>
-      <c r="D10" s="149"/>
-      <c r="E10" s="150"/>
-      <c r="F10" s="150"/>
-      <c r="G10" s="150"/>
-      <c r="H10" s="150"/>
-      <c r="I10" s="150"/>
-      <c r="J10" s="151"/>
-      <c r="K10" s="124"/>
+      <c r="D10" s="175"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="176"/>
+      <c r="G10" s="176"/>
+      <c r="H10" s="176"/>
+      <c r="I10" s="176"/>
+      <c r="J10" s="177"/>
+      <c r="K10" s="123"/>
       <c r="L10" s="38"/>
-      <c r="M10" s="121" t="s">
+      <c r="M10" s="120" t="s">
         <v>10</v>
       </c>
       <c r="N10" s="7"/>
@@ -6038,14 +9571,14 @@
     </row>
     <row r="11" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C11" s="6"/>
-      <c r="D11" s="149"/>
-      <c r="E11" s="150"/>
-      <c r="F11" s="150"/>
-      <c r="G11" s="150"/>
-      <c r="H11" s="150"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="151"/>
-      <c r="K11" s="124"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="177"/>
+      <c r="K11" s="123"/>
       <c r="L11" s="94"/>
       <c r="M11" s="94"/>
       <c r="N11" s="7"/>
@@ -6067,7 +9600,7 @@
       <c r="AF11" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="AG11" s="120">
+      <c r="AG11" s="119">
         <v>0</v>
       </c>
       <c r="AH11" s="78"/>
@@ -6105,15 +9638,15 @@
     </row>
     <row r="12" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C12" s="6"/>
-      <c r="D12" s="149"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="150"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="150"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="151"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="122"/>
+      <c r="D12" s="175"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="176"/>
+      <c r="J12" s="177"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="121"/>
       <c r="M12" s="13" t="s">
         <v>91</v>
       </c>
@@ -6122,10 +9655,10 @@
       <c r="Q12" s="13"/>
       <c r="R12" s="16"/>
       <c r="S12" s="21"/>
-      <c r="T12" s="143" t="s">
+      <c r="T12" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="U12" s="144"/>
+      <c r="U12" s="170"/>
       <c r="V12" s="13"/>
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
@@ -6183,15 +9716,15 @@
     </row>
     <row r="13" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C13" s="6"/>
-      <c r="D13" s="149"/>
-      <c r="E13" s="150"/>
-      <c r="F13" s="150"/>
-      <c r="G13" s="150"/>
-      <c r="H13" s="150"/>
-      <c r="I13" s="150"/>
-      <c r="J13" s="151"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="123"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="176"/>
+      <c r="H13" s="176"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="177"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="122"/>
       <c r="M13" s="13" t="s">
         <v>92</v>
       </c>
@@ -6262,14 +9795,14 @@
     </row>
     <row r="14" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C14" s="6"/>
-      <c r="D14" s="149"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="151"/>
-      <c r="K14" s="124"/>
+      <c r="D14" s="175"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
+      <c r="G14" s="176"/>
+      <c r="H14" s="176"/>
+      <c r="I14" s="176"/>
+      <c r="J14" s="177"/>
+      <c r="K14" s="123"/>
       <c r="L14" s="94"/>
       <c r="M14" s="94"/>
       <c r="N14" s="7"/>
@@ -6288,22 +9821,22 @@
       <c r="AB14" s="51"/>
       <c r="AC14" s="7"/>
       <c r="AE14" s="6"/>
-      <c r="AF14" s="139" t="s">
+      <c r="AF14" s="138" t="s">
         <v>72</v>
       </c>
-      <c r="AG14" s="139" t="str">
+      <c r="AG14" s="138" t="str">
         <f>Q32</f>
         <v>Primary Care</v>
       </c>
-      <c r="AH14" s="139" t="str">
+      <c r="AH14" s="138" t="str">
         <f>Q33</f>
         <v>Hospital Care</v>
       </c>
-      <c r="AI14" s="139" t="str">
+      <c r="AI14" s="138" t="str">
         <f>Q32</f>
         <v>Primary Care</v>
       </c>
-      <c r="AJ14" s="139" t="str">
+      <c r="AJ14" s="138" t="str">
         <f>Q33</f>
         <v>Hospital Care</v>
       </c>
@@ -6349,14 +9882,14 @@
     </row>
     <row r="15" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C15" s="6"/>
-      <c r="D15" s="152"/>
-      <c r="E15" s="153"/>
-      <c r="F15" s="153"/>
-      <c r="G15" s="153"/>
-      <c r="H15" s="153"/>
-      <c r="I15" s="153"/>
-      <c r="J15" s="154"/>
-      <c r="K15" s="124"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="179"/>
+      <c r="F15" s="179"/>
+      <c r="G15" s="179"/>
+      <c r="H15" s="179"/>
+      <c r="I15" s="179"/>
+      <c r="J15" s="180"/>
+      <c r="K15" s="123"/>
       <c r="L15" s="94"/>
       <c r="M15" s="94"/>
       <c r="N15" s="7"/>
@@ -6364,10 +9897,10 @@
       <c r="Q15" s="13"/>
       <c r="R15" s="16"/>
       <c r="S15" s="13"/>
-      <c r="T15" s="144" t="s">
+      <c r="T15" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="U15" s="144"/>
+      <c r="U15" s="170"/>
       <c r="V15" s="13"/>
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
@@ -6651,21 +10184,21 @@
       <c r="I19" s="83">
         <v>0.1</v>
       </c>
-      <c r="J19" s="157" t="s">
+      <c r="J19" s="183" t="s">
         <v>58</v>
       </c>
-      <c r="K19" s="157"/>
-      <c r="L19" s="157"/>
-      <c r="M19" s="157"/>
+      <c r="K19" s="183"/>
+      <c r="L19" s="183"/>
+      <c r="M19" s="183"/>
       <c r="N19" s="30"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="16"/>
       <c r="S19" s="21"/>
-      <c r="T19" s="143" t="s">
+      <c r="T19" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="U19" s="144"/>
+      <c r="U19" s="170"/>
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
@@ -6747,16 +10280,16 @@
       <c r="I20" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="J20" s="125" t="s">
+      <c r="J20" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="K20" s="126" t="s">
+      <c r="K20" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="L20" s="126" t="s">
+      <c r="L20" s="125" t="s">
         <v>62</v>
       </c>
-      <c r="M20" s="127" t="s">
+      <c r="M20" s="126" t="s">
         <v>63</v>
       </c>
       <c r="N20" s="7"/>
@@ -6806,7 +10339,7 @@
     </row>
     <row r="21" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="6"/>
-      <c r="D21" s="155" t="s">
+      <c r="D21" s="181" t="s">
         <v>15</v>
       </c>
       <c r="E21" s="35" t="s">
@@ -6826,7 +10359,7 @@
         <f t="shared" ref="I21:I35" si="1">G21*(1+$I$19)</f>
         <v>0.38500000000000001</v>
       </c>
-      <c r="J21" s="128">
+      <c r="J21" s="127">
         <v>1</v>
       </c>
       <c r="K21" s="60">
@@ -6837,7 +10370,7 @@
         <f>IF(J21=1,COUNTIF($J$21:J21,1)*2,"")</f>
         <v>2</v>
       </c>
-      <c r="M21" s="129">
+      <c r="M21" s="128">
         <f t="shared" ref="M21:M35" si="2">IF(ID=K21,H21,IF(ID=L21,I21,G21))</f>
         <v>0.35</v>
       </c>
@@ -6888,7 +10421,7 @@
     </row>
     <row r="22" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C22" s="6"/>
-      <c r="D22" s="156"/>
+      <c r="D22" s="182"/>
       <c r="E22" s="36" t="s">
         <v>18</v>
       </c>
@@ -6906,7 +10439,7 @@
         <f t="shared" si="1"/>
         <v>0.44000000000000006</v>
       </c>
-      <c r="J22" s="130">
+      <c r="J22" s="129">
         <v>1</v>
       </c>
       <c r="K22" s="34">
@@ -6917,7 +10450,7 @@
         <f>IF(J22=1,COUNTIF($J$21:J22,1)*2,"")</f>
         <v>4</v>
       </c>
-      <c r="M22" s="131">
+      <c r="M22" s="130">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
@@ -6926,10 +10459,10 @@
       <c r="Q22" s="13"/>
       <c r="R22" s="16"/>
       <c r="S22" s="13"/>
-      <c r="T22" s="144" t="s">
+      <c r="T22" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="U22" s="144"/>
+      <c r="U22" s="170"/>
       <c r="V22" s="13"/>
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
@@ -6979,7 +10512,7 @@
     </row>
     <row r="23" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="6"/>
-      <c r="D23" s="156"/>
+      <c r="D23" s="182"/>
       <c r="E23" s="36" t="s">
         <v>20</v>
       </c>
@@ -6997,7 +10530,7 @@
         <f t="shared" si="1"/>
         <v>0.49500000000000005</v>
       </c>
-      <c r="J23" s="130">
+      <c r="J23" s="129">
         <v>1</v>
       </c>
       <c r="K23" s="34">
@@ -7008,7 +10541,7 @@
         <f>IF(J23=1,COUNTIF($J$21:J23,1)*2,"")</f>
         <v>6</v>
       </c>
-      <c r="M23" s="131">
+      <c r="M23" s="130">
         <f t="shared" si="2"/>
         <v>0.45</v>
       </c>
@@ -7059,7 +10592,7 @@
     </row>
     <row r="24" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C24" s="6"/>
-      <c r="D24" s="141" t="s">
+      <c r="D24" s="167" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="37" t="s">
@@ -7079,7 +10612,7 @@
         <f t="shared" si="1"/>
         <v>3333.0000000000005</v>
       </c>
-      <c r="J24" s="132">
+      <c r="J24" s="131">
         <v>1</v>
       </c>
       <c r="K24" s="56">
@@ -7090,7 +10623,7 @@
         <f>IF(J24=1,COUNTIF($J$21:J24,1)*2,"")</f>
         <v>8</v>
       </c>
-      <c r="M24" s="133">
+      <c r="M24" s="132">
         <f t="shared" si="2"/>
         <v>3030</v>
       </c>
@@ -7143,7 +10676,7 @@
     </row>
     <row r="25" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="6"/>
-      <c r="D25" s="141"/>
+      <c r="D25" s="167"/>
       <c r="E25" s="37" t="s">
         <v>24</v>
       </c>
@@ -7161,7 +10694,7 @@
         <f t="shared" si="1"/>
         <v>13222.000000000002</v>
       </c>
-      <c r="J25" s="132">
+      <c r="J25" s="131">
         <v>1</v>
       </c>
       <c r="K25" s="56">
@@ -7172,7 +10705,7 @@
         <f>IF(J25=1,COUNTIF($J$21:J25,1)*2,"")</f>
         <v>10</v>
       </c>
-      <c r="M25" s="133">
+      <c r="M25" s="132">
         <f t="shared" si="2"/>
         <v>12020</v>
       </c>
@@ -7223,7 +10756,7 @@
     </row>
     <row r="26" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C26" s="6"/>
-      <c r="D26" s="141"/>
+      <c r="D26" s="167"/>
       <c r="E26" s="37" t="s">
         <v>26</v>
       </c>
@@ -7241,7 +10774,7 @@
         <f t="shared" si="1"/>
         <v>4290</v>
       </c>
-      <c r="J26" s="132">
+      <c r="J26" s="131">
         <v>1</v>
       </c>
       <c r="K26" s="56">
@@ -7252,7 +10785,7 @@
         <f>IF(J26=1,COUNTIF($J$21:J26,1)*2,"")</f>
         <v>12</v>
       </c>
-      <c r="M26" s="133">
+      <c r="M26" s="132">
         <f t="shared" si="2"/>
         <v>3900</v>
       </c>
@@ -7261,10 +10794,10 @@
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
       <c r="S26" s="16"/>
-      <c r="T26" s="143" t="s">
+      <c r="T26" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="U26" s="144"/>
+      <c r="U26" s="170"/>
       <c r="V26" s="13"/>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
@@ -7319,7 +10852,7 @@
     </row>
     <row r="27" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C27" s="6"/>
-      <c r="D27" s="141"/>
+      <c r="D27" s="167"/>
       <c r="E27" s="37" t="s">
         <v>28</v>
       </c>
@@ -7337,7 +10870,7 @@
         <f t="shared" si="1"/>
         <v>14080.000000000002</v>
       </c>
-      <c r="J27" s="132">
+      <c r="J27" s="131">
         <v>1</v>
       </c>
       <c r="K27" s="56">
@@ -7348,7 +10881,7 @@
         <f>IF(J27=1,COUNTIF($J$21:J27,1)*2,"")</f>
         <v>14</v>
       </c>
-      <c r="M27" s="133">
+      <c r="M27" s="132">
         <f t="shared" si="2"/>
         <v>12800</v>
       </c>
@@ -7400,7 +10933,7 @@
     </row>
     <row r="28" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="6"/>
-      <c r="D28" s="141"/>
+      <c r="D28" s="167"/>
       <c r="E28" s="37" t="s">
         <v>30</v>
       </c>
@@ -7418,7 +10951,7 @@
         <f t="shared" si="1"/>
         <v>6820.0000000000009</v>
       </c>
-      <c r="J28" s="132">
+      <c r="J28" s="131">
         <v>1</v>
       </c>
       <c r="K28" s="56">
@@ -7429,7 +10962,7 @@
         <f>IF(J28=1,COUNTIF($J$21:J28,1)*2,"")</f>
         <v>16</v>
       </c>
-      <c r="M28" s="133">
+      <c r="M28" s="132">
         <f t="shared" si="2"/>
         <v>6200</v>
       </c>
@@ -7485,7 +11018,7 @@
     </row>
     <row r="29" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="6"/>
-      <c r="D29" s="141"/>
+      <c r="D29" s="167"/>
       <c r="E29" s="37" t="s">
         <v>32</v>
       </c>
@@ -7503,7 +11036,7 @@
         <f t="shared" si="1"/>
         <v>15840.000000000002</v>
       </c>
-      <c r="J29" s="132">
+      <c r="J29" s="131">
         <v>1</v>
       </c>
       <c r="K29" s="56">
@@ -7514,7 +11047,7 @@
         <f>IF(J29=1,COUNTIF($J$21:J29,1)*2,"")</f>
         <v>18</v>
       </c>
-      <c r="M29" s="133">
+      <c r="M29" s="132">
         <f t="shared" si="2"/>
         <v>14400</v>
       </c>
@@ -7568,7 +11101,7 @@
     </row>
     <row r="30" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C30" s="6"/>
-      <c r="D30" s="142" t="s">
+      <c r="D30" s="168" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="39" t="s">
@@ -7588,7 +11121,7 @@
         <f t="shared" si="1"/>
         <v>7.7000000000000011</v>
       </c>
-      <c r="J30" s="134">
+      <c r="J30" s="133">
         <v>1</v>
       </c>
       <c r="K30" s="38">
@@ -7599,7 +11132,7 @@
         <f>IF(J30=1,COUNTIF($J$21:J30,1)*2,"")</f>
         <v>20</v>
       </c>
-      <c r="M30" s="135">
+      <c r="M30" s="134">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -7663,7 +11196,7 @@
     </row>
     <row r="31" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C31" s="6"/>
-      <c r="D31" s="142"/>
+      <c r="D31" s="168"/>
       <c r="E31" s="39" t="s">
         <v>36</v>
       </c>
@@ -7681,7 +11214,7 @@
         <f t="shared" si="1"/>
         <v>1.6500000000000001</v>
       </c>
-      <c r="J31" s="134">
+      <c r="J31" s="133">
         <v>1</v>
       </c>
       <c r="K31" s="38">
@@ -7692,7 +11225,7 @@
         <f>IF(J31=1,COUNTIF($J$21:J31,1)*2,"")</f>
         <v>22</v>
       </c>
-      <c r="M31" s="135">
+      <c r="M31" s="134">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
@@ -7712,8 +11245,8 @@
       </c>
       <c r="T31" s="162"/>
       <c r="U31" s="163"/>
-      <c r="V31" s="164"/>
-      <c r="W31" s="119"/>
+      <c r="V31" s="163"/>
+      <c r="W31" s="164"/>
       <c r="X31" s="14"/>
       <c r="Y31" s="14"/>
       <c r="Z31" s="14"/>
@@ -7752,7 +11285,7 @@
     </row>
     <row r="32" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C32" s="6"/>
-      <c r="D32" s="142"/>
+      <c r="D32" s="168"/>
       <c r="E32" s="39" t="s">
         <v>38</v>
       </c>
@@ -7770,7 +11303,7 @@
         <f t="shared" si="1"/>
         <v>7.7000000000000011</v>
       </c>
-      <c r="J32" s="134">
+      <c r="J32" s="133">
         <v>1</v>
       </c>
       <c r="K32" s="38">
@@ -7781,7 +11314,7 @@
         <f>IF(J32=1,COUNTIF($J$21:J32,1)*2,"")</f>
         <v>24</v>
       </c>
-      <c r="M32" s="135">
+      <c r="M32" s="134">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -7853,7 +11386,7 @@
     </row>
     <row r="33" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C33" s="6"/>
-      <c r="D33" s="142"/>
+      <c r="D33" s="168"/>
       <c r="E33" s="39" t="s">
         <v>40</v>
       </c>
@@ -7871,7 +11404,7 @@
         <f t="shared" si="1"/>
         <v>1.6500000000000001</v>
       </c>
-      <c r="J33" s="134">
+      <c r="J33" s="133">
         <v>1</v>
       </c>
       <c r="K33" s="38">
@@ -7882,7 +11415,7 @@
         <f>IF(J33=1,COUNTIF($J$21:J33,1)*2,"")</f>
         <v>26</v>
       </c>
-      <c r="M33" s="135">
+      <c r="M33" s="134">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
@@ -7954,7 +11487,7 @@
     </row>
     <row r="34" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C34" s="6"/>
-      <c r="D34" s="142"/>
+      <c r="D34" s="168"/>
       <c r="E34" s="39" t="s">
         <v>42</v>
       </c>
@@ -7972,7 +11505,7 @@
         <f t="shared" si="1"/>
         <v>7.7000000000000011</v>
       </c>
-      <c r="J34" s="134">
+      <c r="J34" s="133">
         <v>1</v>
       </c>
       <c r="K34" s="38">
@@ -7983,7 +11516,7 @@
         <f>IF(J34=1,COUNTIF($J$21:J34,1)*2,"")</f>
         <v>28</v>
       </c>
-      <c r="M34" s="135">
+      <c r="M34" s="134">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -8038,7 +11571,7 @@
     </row>
     <row r="35" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C35" s="6"/>
-      <c r="D35" s="142"/>
+      <c r="D35" s="168"/>
       <c r="E35" s="39" t="s">
         <v>44</v>
       </c>
@@ -8056,18 +11589,18 @@
         <f t="shared" si="1"/>
         <v>1.6500000000000001</v>
       </c>
-      <c r="J35" s="136">
+      <c r="J35" s="135">
         <v>1</v>
       </c>
-      <c r="K35" s="137">
+      <c r="K35" s="136">
         <f>IF(J35=1,COUNTIF($J$21:J35,1)*2-1,"")</f>
         <v>29</v>
       </c>
-      <c r="L35" s="137">
+      <c r="L35" s="136">
         <f>IF(J35=1,COUNTIF($J$21:J35,1)*2,"")</f>
         <v>30</v>
       </c>
-      <c r="M35" s="138">
+      <c r="M35" s="137">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
@@ -8928,19 +12461,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="AP8:AV8"/>
-    <mergeCell ref="AP34:AV34"/>
-    <mergeCell ref="AM12:AN12"/>
-    <mergeCell ref="AK11:AN11"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="T31:V31"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AI13:AJ13"/>
-    <mergeCell ref="AG13:AH13"/>
-    <mergeCell ref="D24:D29"/>
-    <mergeCell ref="D30:D35"/>
-    <mergeCell ref="T12:U12"/>
     <mergeCell ref="C1:N3"/>
     <mergeCell ref="D7:J15"/>
     <mergeCell ref="D21:D23"/>
@@ -8950,6 +12470,19 @@
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="L6:M7"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="AP8:AV8"/>
+    <mergeCell ref="D24:D29"/>
+    <mergeCell ref="D30:D35"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="AP34:AV34"/>
+    <mergeCell ref="AM12:AN12"/>
+    <mergeCell ref="AK11:AN11"/>
+    <mergeCell ref="T31:W31"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AI13:AJ13"/>
+    <mergeCell ref="AG13:AH13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8962,6 +12495,3395 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3C63F4-8CA6-6246-918B-7A6D37273AB3}">
+  <dimension ref="C1:AW59"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.83203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="2.33203125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="2.83203125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="36.83203125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="12" customWidth="1"/>
+    <col min="7" max="9" width="12.83203125" style="12" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" style="12" customWidth="1"/>
+    <col min="12" max="13" width="13.33203125" style="12" customWidth="1"/>
+    <col min="14" max="14" width="2.83203125" style="12" customWidth="1"/>
+    <col min="15" max="15" width="6.83203125" style="12" customWidth="1"/>
+    <col min="16" max="16" width="2.83203125" style="12" customWidth="1"/>
+    <col min="17" max="17" width="13" style="12" customWidth="1"/>
+    <col min="18" max="23" width="14.83203125" style="12" customWidth="1"/>
+    <col min="24" max="24" width="3.33203125" style="12" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" style="12"/>
+    <col min="26" max="26" width="4.6640625" style="12" customWidth="1"/>
+    <col min="27" max="28" width="14.83203125" style="12"/>
+    <col min="29" max="29" width="2.83203125" style="12" customWidth="1"/>
+    <col min="30" max="30" width="6.83203125" style="12" customWidth="1"/>
+    <col min="31" max="31" width="2.83203125" style="12" customWidth="1"/>
+    <col min="32" max="32" width="47.6640625" style="64" customWidth="1"/>
+    <col min="33" max="38" width="12.83203125" style="64" customWidth="1"/>
+    <col min="39" max="39" width="2.83203125" style="12" customWidth="1"/>
+    <col min="40" max="40" width="14.83203125" style="12"/>
+    <col min="41" max="41" width="2.83203125" style="12" customWidth="1"/>
+    <col min="42" max="48" width="16.33203125" style="12" customWidth="1"/>
+    <col min="49" max="49" width="2.83203125" style="12" customWidth="1"/>
+    <col min="50" max="16384" width="14.83203125" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:49" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C1" s="171" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="86"/>
+      <c r="AG1" s="86"/>
+      <c r="AH1" s="86"/>
+      <c r="AI1" s="86"/>
+      <c r="AJ1" s="86"/>
+      <c r="AK1" s="86"/>
+      <c r="AL1" s="86"/>
+      <c r="AM1" s="26"/>
+    </row>
+    <row r="2" spans="3:49" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="86"/>
+      <c r="AG2" s="86"/>
+      <c r="AH2" s="86"/>
+      <c r="AI2" s="86"/>
+      <c r="AJ2" s="86"/>
+      <c r="AK2" s="86"/>
+      <c r="AL2" s="86"/>
+      <c r="AM2" s="26"/>
+    </row>
+    <row r="3" spans="3:49" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="171"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
+      <c r="AA3" s="26"/>
+      <c r="AB3" s="26"/>
+      <c r="AC3" s="26"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="86"/>
+      <c r="AG3" s="86"/>
+      <c r="AH3" s="86"/>
+      <c r="AI3" s="86"/>
+      <c r="AJ3" s="86"/>
+      <c r="AK3" s="86"/>
+      <c r="AL3" s="86"/>
+      <c r="AM3" s="26"/>
+    </row>
+    <row r="5" spans="3:49" s="11" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="4"/>
+      <c r="D5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="1"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="1"/>
+      <c r="AE5" s="4"/>
+      <c r="AF5" s="65" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG5" s="85"/>
+      <c r="AH5" s="85"/>
+      <c r="AI5" s="85"/>
+      <c r="AJ5" s="85"/>
+      <c r="AK5" s="85"/>
+      <c r="AL5" s="85"/>
+      <c r="AM5" s="1"/>
+      <c r="AO5" s="4"/>
+      <c r="AP5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AQ5" s="3"/>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="2"/>
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="1"/>
+    </row>
+    <row r="6" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="6"/>
+      <c r="D6" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="184" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="184"/>
+      <c r="N6" s="7"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="141"/>
+      <c r="Z6" s="141"/>
+      <c r="AA6" s="185"/>
+      <c r="AB6" s="185"/>
+      <c r="AC6" s="7"/>
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG6" s="61"/>
+      <c r="AH6" s="61"/>
+      <c r="AI6" s="61"/>
+      <c r="AJ6" s="61"/>
+      <c r="AK6" s="61"/>
+      <c r="AL6" s="61"/>
+      <c r="AM6" s="7"/>
+      <c r="AO6" s="6"/>
+      <c r="AP6" s="13"/>
+      <c r="AQ6" s="13"/>
+      <c r="AR6" s="13"/>
+      <c r="AS6" s="13"/>
+      <c r="AT6" s="13"/>
+      <c r="AU6" s="13"/>
+      <c r="AV6" s="13"/>
+      <c r="AW6" s="7"/>
+    </row>
+    <row r="7" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="6"/>
+      <c r="D7" s="172" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="173"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="173"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="174"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="184"/>
+      <c r="M7" s="184"/>
+      <c r="N7" s="7"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="139" t="s">
+        <v>94</v>
+      </c>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="104"/>
+      <c r="Z7" s="104"/>
+      <c r="AA7" s="104"/>
+      <c r="AB7" s="104"/>
+      <c r="AC7" s="7"/>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="109" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG7" s="61"/>
+      <c r="AH7" s="61"/>
+      <c r="AI7" s="61"/>
+      <c r="AJ7" s="61"/>
+      <c r="AK7" s="61"/>
+      <c r="AL7" s="61"/>
+      <c r="AM7" s="7"/>
+      <c r="AO7" s="6"/>
+      <c r="AP7" s="158" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ7" s="14"/>
+      <c r="AR7" s="14"/>
+      <c r="AS7" s="14"/>
+      <c r="AT7" s="14"/>
+      <c r="AU7" s="14"/>
+      <c r="AV7" s="14"/>
+      <c r="AW7" s="7"/>
+    </row>
+    <row r="8" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="6"/>
+      <c r="D8" s="175"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="177"/>
+      <c r="K8" s="123"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="120" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" s="7"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="170" t="s">
+        <v>6</v>
+      </c>
+      <c r="U8" s="170"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="142"/>
+      <c r="Z8" s="104"/>
+      <c r="AA8" s="78"/>
+      <c r="AB8" s="143"/>
+      <c r="AC8" s="7"/>
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="159" t="str">
+        <f>Q32&amp;" vs "&amp;Q31</f>
+        <v>Primary Care vs Routine Practice</v>
+      </c>
+      <c r="AG8" s="159"/>
+      <c r="AH8" s="159"/>
+      <c r="AI8" s="159"/>
+      <c r="AJ8" s="159"/>
+      <c r="AK8" s="159"/>
+      <c r="AL8" s="159"/>
+      <c r="AM8" s="7"/>
+      <c r="AO8" s="6"/>
+      <c r="AP8" s="157" t="str" cm="1">
+        <f t="array" ref="AP8:AV41">_xlfn.LET(
+    _xlpm.names,$F$21:$F$35,
+    _xlpm.desc,$E$21:$E$35,
+    _xlpm.base,$G$21:$G$35,
+    _xlpm.low,$H$21:$H$35,
+    _xlpm.high,$I$21:$I$35,
+    _xlpm.inc,$J$21:$J$35,
+    _xlpm.idx,_xlfn.SEQUENCE(ROWS(_xlpm.base)),
+    _xlpm.OWSA,_xlfn.LAMBDA(_xlpm.rowNum,_xlpm.exclude,
+        _xlfn.LET(
+            _xlpm.label,_xlpm.desc&amp;" ("&amp;
+                TEXT(_xlpm.low,"#,##0.###")&amp;", "&amp;
+                TEXT(_xlpm.high,"#,##0.###")&amp;")",
+            _xlpm.llI,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+                INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.low,_xlpm.i),_xlpm.base)),_xlpm.rowNum,5)
+            )),
+            _xlpm.ulI,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+                INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.high,_xlpm.i),_xlpm.base)),_xlpm.rowNum,5)
+            )),
+            _xlpm.llN,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+                INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.low,_xlpm.i),_xlpm.base)),_xlpm.rowNum,6)
+            )),
+            _xlpm.ulN,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+                INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.high,_xlpm.i),_xlpm.base)),_xlpm.rowNum,6)
+            )),
+            _xlpm.results,_xlfn.HSTACK(
+                _xlpm.label,
+                _xlpm.llI,
+                _xlpm.ulI,
+                ABS(_xlpm.ulI-_xlpm.llI),
+                _xlpm.llN,
+                _xlpm.ulN,
+                ABS(_xlpm.ulN-_xlpm.llN)
+            ),
+            _xlpm.selected,_xlfn._xlws.FILTER(
+                _xlpm.results,
+                (_xlpm.inc=1)*(LEFT(_xlpm.names,2)&lt;&gt;_xlpm.exclude)
+            ),
+            _xlfn.SORTBY(_xlpm.selected,_xlfn.CHOOSECOLS(_xlpm.selected,7),-1)
+        )
+    ),
+    _xlpm.resultBase,Tree(_xlpm.base),
+    _xlpm.resultPC,_xlpm.OWSA(2,"HC"),
+    _xlpm.resultHC,_xlpm.OWSA(3,"RP"),
+    _xlpm.blank4,_xlfn.MAKEARRAY(4,7,_xlfn.LAMBDA(_xlpm.rowNum,_xlpm.colNum,"")),
+    _xlpm.blank2,_xlfn.MAKEARRAY(2,7,_xlfn.LAMBDA(_xlpm.rowNum,_xlpm.colNum,"")),
+    _xlpm.headerBase,_xlfn.HSTACK(
+        "Strategy",
+        "Expected Cost",
+        "Expected Outcome",
+        "Incremental Cost",
+        "Incremental Outcome",
+        "ICER",
+        "INMB"
+    ),
+    _xlpm.headerOWSA,_xlfn.HSTACK(
+        "Parameter",
+        "ICER LL",
+        "ICER UL",
+        "ABS ICER",
+        "INMB LL",
+        "INMB UL",
+        "ABS INMB"
+    ),
+    _xlfn.VSTACK(
+        _xlpm.headerBase,
+        _xlfn.HSTACK(
+            {"Routine Practice";"Primary Care";"Hospital Care"},
+            _xlpm.resultBase
+        ),
+        _xlpm.blank4,
+        _xlfn.HSTACK("Primary Care vs Routine Practice","","","","","",""),
+        _xlpm.headerOWSA,
+        _xlpm.resultPC,
+        _xlpm.blank2,
+        _xlfn.HSTACK("Hospital Care vs Primary Care","","","","","",""),
+        _xlpm.headerOWSA,
+        _xlpm.resultHC
+    )
+)</f>
+        <v>Strategy</v>
+      </c>
+      <c r="AQ8" s="88" t="str">
+        <v>Expected Cost</v>
+      </c>
+      <c r="AR8" s="88" t="str">
+        <v>Expected Outcome</v>
+      </c>
+      <c r="AS8" s="88" t="str">
+        <v>Incremental Cost</v>
+      </c>
+      <c r="AT8" s="88" t="str">
+        <v>Incremental Outcome</v>
+      </c>
+      <c r="AU8" s="88" t="str">
+        <v>ICER</v>
+      </c>
+      <c r="AV8" s="88" t="str">
+        <v>INMB</v>
+      </c>
+      <c r="AW8" s="7"/>
+    </row>
+    <row r="9" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="6"/>
+      <c r="D9" s="175"/>
+      <c r="E9" s="176"/>
+      <c r="F9" s="176"/>
+      <c r="G9" s="176"/>
+      <c r="H9" s="176"/>
+      <c r="I9" s="176"/>
+      <c r="J9" s="177"/>
+      <c r="K9" s="123"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="120" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" s="7"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="142"/>
+      <c r="Z9" s="104"/>
+      <c r="AA9" s="140"/>
+      <c r="AB9" s="143"/>
+      <c r="AC9" s="7"/>
+      <c r="AE9" s="6"/>
+      <c r="AF9" s="84" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG9" s="84" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH9" s="84" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI9" s="84" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ9" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK9" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL9" s="84" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM9" s="7"/>
+      <c r="AO9" s="6"/>
+      <c r="AP9" s="43" t="str">
+        <v>Routine Practice</v>
+      </c>
+      <c r="AQ9" s="70">
+        <v>8873.5</v>
+      </c>
+      <c r="AR9" s="52">
+        <v>3.4249999999999998</v>
+      </c>
+      <c r="AS9" s="144">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="145">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="145">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="146">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="7"/>
+    </row>
+    <row r="10" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="6"/>
+      <c r="D10" s="175"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="176"/>
+      <c r="G10" s="176"/>
+      <c r="H10" s="176"/>
+      <c r="I10" s="176"/>
+      <c r="J10" s="177"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="120" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="7"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="142"/>
+      <c r="Z10" s="104"/>
+      <c r="AA10" s="140"/>
+      <c r="AB10" s="143"/>
+      <c r="AC10" s="7"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="105" t="str" cm="1">
+        <f t="array" ref="AF10:AL19">_xlfn.LET(
+    _xlpm.names,$F$21:$F$35,
+    _xlpm.desc,$E$21:$E$35,
+    _xlpm.base,$G$21:$G$35,
+    _xlpm.low,$H$21:$H$35,
+    _xlpm.high,$I$21:$I$35,
+    _xlpm.inc,$J$21:$J$35,
+    _xlpm.idx,_xlfn.SEQUENCE(ROWS(_xlpm.base)),
+    _xlpm.label,_xlpm.desc&amp;" ("&amp;TEXT(_xlpm.low,"#,##0.###")&amp;", "&amp;TEXT(_xlpm.high,"#,##0.###")&amp;")",
+    _xlpm.llI,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+        INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.low,_xlpm.i),_xlpm.base)),2,5)
+    )),
+    _xlpm.ulI,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+        INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.high,_xlpm.i),_xlpm.base)),2,5)
+    )),
+    _xlpm.llN,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+        INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.low,_xlpm.i),_xlpm.base)),2,6)
+    )),
+    _xlpm.ulN,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+        INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.high,_xlpm.i),_xlpm.base)),2,6)
+    )),
+    _xlpm.data,_xlfn.HSTACK(
+        _xlpm.label,_xlpm.llI,_xlpm.ulI,ABS(_xlpm.ulI-_xlpm.llI),
+        _xlpm.llN,_xlpm.ulN,ABS(_xlpm.ulN-_xlpm.llN)
+    ),
+    _xlpm.result,_xlfn._xlws.FILTER(_xlpm.data,(_xlpm.inc=1)*(LEFT(_xlpm.names,2)&lt;&gt;"HC")),
+    _xlfn.SORTBY(_xlpm.result,_xlfn.CHOOSECOLS(_xlpm.result,7),-1)
+)</f>
+        <v>Life expectancy of early detection in primary care (6.3, 7.7)</v>
+      </c>
+      <c r="AG10" s="103">
+        <v>-73300.000000001557</v>
+      </c>
+      <c r="AH10" s="103">
+        <v>660.36036036035966</v>
+      </c>
+      <c r="AI10" s="103">
+        <v>73960.360360361912</v>
+      </c>
+      <c r="AJ10" s="103">
+        <v>-466.49999999999784</v>
+      </c>
+      <c r="AK10" s="103">
+        <v>10733.500000000013</v>
+      </c>
+      <c r="AL10" s="103">
+        <v>11200.000000000011</v>
+      </c>
+      <c r="AM10" s="7"/>
+      <c r="AO10" s="6"/>
+      <c r="AP10" s="43" t="str">
+        <v>Primary Care</v>
+      </c>
+      <c r="AQ10" s="70">
+        <v>9240</v>
+      </c>
+      <c r="AR10" s="52">
+        <v>3.7</v>
+      </c>
+      <c r="AS10" s="70">
+        <v>366.5</v>
+      </c>
+      <c r="AT10" s="34">
+        <v>0.27500000000000036</v>
+      </c>
+      <c r="AU10" s="118">
+        <v>1332.7272727272709</v>
+      </c>
+      <c r="AV10" s="118">
+        <v>5133.5000000000073</v>
+      </c>
+      <c r="AW10" s="7"/>
+    </row>
+    <row r="11" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="6"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="177"/>
+      <c r="K11" s="123"/>
+      <c r="L11" s="94"/>
+      <c r="M11" s="94"/>
+      <c r="N11" s="7"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="23"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="142"/>
+      <c r="Z11" s="104"/>
+      <c r="AA11" s="140"/>
+      <c r="AB11" s="143"/>
+      <c r="AC11" s="7"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="105" t="str">
+        <v>Life expectancy of early detection in routine practice (6.3, 7.7)</v>
+      </c>
+      <c r="AG11" s="103">
+        <v>704.8076923076917</v>
+      </c>
+      <c r="AH11" s="103">
+        <v>12216.666666666746</v>
+      </c>
+      <c r="AI11" s="103">
+        <v>11511.858974359055</v>
+      </c>
+      <c r="AJ11" s="103">
+        <v>10033.500000000009</v>
+      </c>
+      <c r="AK11" s="103">
+        <v>233.49999999999613</v>
+      </c>
+      <c r="AL11" s="103">
+        <v>9800.0000000000127</v>
+      </c>
+      <c r="AM11" s="7"/>
+      <c r="AO11" s="6"/>
+      <c r="AP11" s="43" t="str">
+        <v>Hospital Care</v>
+      </c>
+      <c r="AQ11" s="70">
+        <v>10710</v>
+      </c>
+      <c r="AR11" s="52">
+        <v>3.9750000000000001</v>
+      </c>
+      <c r="AS11" s="70">
+        <v>1470</v>
+      </c>
+      <c r="AT11" s="52">
+        <v>0.27499999999999991</v>
+      </c>
+      <c r="AU11" s="118">
+        <v>5345.4545454545469</v>
+      </c>
+      <c r="AV11" s="118">
+        <v>4029.9999999999982</v>
+      </c>
+      <c r="AW11" s="7"/>
+    </row>
+    <row r="12" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="6"/>
+      <c r="D12" s="175"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="176"/>
+      <c r="J12" s="177"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="N12" s="7"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="169" t="s">
+        <v>7</v>
+      </c>
+      <c r="U12" s="170"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="142"/>
+      <c r="Z12" s="104"/>
+      <c r="AA12" s="78"/>
+      <c r="AB12" s="143"/>
+      <c r="AC12" s="7"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="105" t="str">
+        <v>Probability of early detection in primary care (0.36, 0.44)</v>
+      </c>
+      <c r="AG12" s="103">
+        <v>13136.363636363492</v>
+      </c>
+      <c r="AH12" s="103">
+        <v>21.21212121212119</v>
+      </c>
+      <c r="AI12" s="103">
+        <v>13115.15151515137</v>
+      </c>
+      <c r="AJ12" s="103">
+        <v>377.50000000001205</v>
+      </c>
+      <c r="AK12" s="103">
+        <v>9889.5000000000109</v>
+      </c>
+      <c r="AL12" s="103">
+        <v>9511.9999999999982</v>
+      </c>
+      <c r="AM12" s="7"/>
+      <c r="AO12" s="6"/>
+      <c r="AP12" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AQ12" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AR12" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AS12" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AT12" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AU12" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AV12" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AW12" s="7"/>
+    </row>
+    <row r="13" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="6"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="176"/>
+      <c r="H13" s="176"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="177"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="N13" s="7"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="142"/>
+      <c r="Z13" s="104"/>
+      <c r="AA13" s="140"/>
+      <c r="AB13" s="143"/>
+      <c r="AC13" s="7"/>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="105" t="str">
+        <v>Probability of early detection in routine practice (0.315, 0.385)</v>
+      </c>
+      <c r="AG13" s="103">
+        <v>110.90909090908774</v>
+      </c>
+      <c r="AH13" s="103">
+        <v>8256.3636363636306</v>
+      </c>
+      <c r="AI13" s="103">
+        <v>8145.4545454545432</v>
+      </c>
+      <c r="AJ13" s="103">
+        <v>9298.1500000000069</v>
+      </c>
+      <c r="AK13" s="103">
+        <v>968.85000000000082</v>
+      </c>
+      <c r="AL13" s="103">
+        <v>8329.3000000000065</v>
+      </c>
+      <c r="AM13" s="7"/>
+      <c r="AO13" s="6"/>
+      <c r="AP13" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AQ13" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AR13" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AS13" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AT13" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AU13" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AV13" s="13" t="str">
+        <v/>
+      </c>
+      <c r="AW13" s="7"/>
+    </row>
+    <row r="14" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="6"/>
+      <c r="D14" s="175"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="176"/>
+      <c r="G14" s="176"/>
+      <c r="H14" s="176"/>
+      <c r="I14" s="176"/>
+      <c r="J14" s="177"/>
+      <c r="K14" s="123"/>
+      <c r="L14" s="94"/>
+      <c r="M14" s="94"/>
+      <c r="N14" s="7"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="142"/>
+      <c r="Z14" s="104"/>
+      <c r="AA14" s="140"/>
+      <c r="AB14" s="143"/>
+      <c r="AC14" s="7"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="105" t="str">
+        <v>Life expectancy of late detection in routine practice (1.35, 1.65)</v>
+      </c>
+      <c r="AG14" s="103">
+        <v>983.89261744966313</v>
+      </c>
+      <c r="AH14" s="103">
+        <v>2064.7887323943637</v>
+      </c>
+      <c r="AI14" s="103">
+        <v>1080.8961149447005</v>
+      </c>
+      <c r="AJ14" s="103">
+        <v>7083.50000000001</v>
+      </c>
+      <c r="AK14" s="103">
+        <v>3183.5000000000041</v>
+      </c>
+      <c r="AL14" s="103">
+        <v>3900.0000000000059</v>
+      </c>
+      <c r="AM14" s="7"/>
+      <c r="AO14" s="55"/>
+      <c r="AP14" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AQ14" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AR14" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AS14" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AT14" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AU14" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AV14" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AW14" s="42"/>
+    </row>
+    <row r="15" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="6"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="179"/>
+      <c r="F15" s="179"/>
+      <c r="G15" s="179"/>
+      <c r="H15" s="179"/>
+      <c r="I15" s="179"/>
+      <c r="J15" s="180"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="94"/>
+      <c r="N15" s="7"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="170" t="s">
+        <v>6</v>
+      </c>
+      <c r="U15" s="170"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="142"/>
+      <c r="Z15" s="104"/>
+      <c r="AA15" s="78"/>
+      <c r="AB15" s="143"/>
+      <c r="AC15" s="7"/>
+      <c r="AE15" s="6"/>
+      <c r="AF15" s="105" t="str">
+        <v>Life expectancy of late detection in primary care (1.35, 1.65)</v>
+      </c>
+      <c r="AG15" s="103">
+        <v>1981.0810810810758</v>
+      </c>
+      <c r="AH15" s="103">
+        <v>1004.1095890410953</v>
+      </c>
+      <c r="AI15" s="103">
+        <v>976.97149203998049</v>
+      </c>
+      <c r="AJ15" s="103">
+        <v>3333.50000000001</v>
+      </c>
+      <c r="AK15" s="103">
+        <v>6933.5000000000045</v>
+      </c>
+      <c r="AL15" s="103">
+        <v>3599.9999999999945</v>
+      </c>
+      <c r="AM15" s="7"/>
+      <c r="AO15" s="55"/>
+      <c r="AP15" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AQ15" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AR15" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AS15" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AT15" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AU15" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AV15" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AW15" s="42"/>
+    </row>
+    <row r="16" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="10"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="13"/>
+      <c r="U16" s="13"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="13"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="142"/>
+      <c r="Z16" s="104"/>
+      <c r="AA16" s="140"/>
+      <c r="AB16" s="143"/>
+      <c r="AC16" s="7"/>
+      <c r="AE16" s="6"/>
+      <c r="AF16" s="105" t="str">
+        <v>Cost of late detection in routine practice (10,818., 13,222.)</v>
+      </c>
+      <c r="AG16" s="103">
+        <v>4173.8181818181774</v>
+      </c>
+      <c r="AH16" s="103">
+        <v>-1508.3636363636383</v>
+      </c>
+      <c r="AI16" s="103">
+        <v>5682.1818181818162</v>
+      </c>
+      <c r="AJ16" s="103">
+        <v>4352.2000000000071</v>
+      </c>
+      <c r="AK16" s="103">
+        <v>5914.8000000000084</v>
+      </c>
+      <c r="AL16" s="103">
+        <v>1562.6000000000013</v>
+      </c>
+      <c r="AM16" s="7"/>
+      <c r="AO16" s="55"/>
+      <c r="AP16" s="159" t="str">
+        <v>Primary Care vs Routine Practice</v>
+      </c>
+      <c r="AQ16" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AR16" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AS16" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AT16" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AU16" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AV16" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AW16" s="42"/>
+    </row>
+    <row r="17" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="P17" s="6"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="T17" s="19"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="142"/>
+      <c r="Z17" s="104"/>
+      <c r="AA17" s="140"/>
+      <c r="AB17" s="143"/>
+      <c r="AC17" s="7"/>
+      <c r="AE17" s="6"/>
+      <c r="AF17" s="105" t="str">
+        <v>Cost of late detection in primary care (11,520., 14,080.)</v>
+      </c>
+      <c r="AG17" s="103">
+        <v>-1459.9999999999982</v>
+      </c>
+      <c r="AH17" s="103">
+        <v>4125.4545454545405</v>
+      </c>
+      <c r="AI17" s="103">
+        <v>5585.4545454545387</v>
+      </c>
+      <c r="AJ17" s="103">
+        <v>5901.5000000000073</v>
+      </c>
+      <c r="AK17" s="103">
+        <v>4365.5000000000073</v>
+      </c>
+      <c r="AL17" s="103">
+        <v>1536</v>
+      </c>
+      <c r="AM17" s="7"/>
+      <c r="AO17" s="55"/>
+      <c r="AP17" s="84" t="str">
+        <v>Parameter</v>
+      </c>
+      <c r="AQ17" s="84" t="str">
+        <v>ICER LL</v>
+      </c>
+      <c r="AR17" s="84" t="str">
+        <v>ICER UL</v>
+      </c>
+      <c r="AS17" s="84" t="str">
+        <v>ABS ICER</v>
+      </c>
+      <c r="AT17" s="84" t="str">
+        <v>INMB LL</v>
+      </c>
+      <c r="AU17" s="84" t="str">
+        <v>INMB UL</v>
+      </c>
+      <c r="AV17" s="84" t="str">
+        <v>ABS INMB</v>
+      </c>
+      <c r="AW17" s="42"/>
+    </row>
+    <row r="18" spans="3:49" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="4"/>
+      <c r="D18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="1"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="18"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="142"/>
+      <c r="Z18" s="104"/>
+      <c r="AA18" s="140"/>
+      <c r="AB18" s="143"/>
+      <c r="AC18" s="7"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="105" t="str">
+        <v>Cost of early detection in primary care (3,510., 4,290.)</v>
+      </c>
+      <c r="AG18" s="103">
+        <v>765.45454545454447</v>
+      </c>
+      <c r="AH18" s="103">
+        <v>1899.9999999999975</v>
+      </c>
+      <c r="AI18" s="103">
+        <v>1134.5454545454531</v>
+      </c>
+      <c r="AJ18" s="103">
+        <v>5289.5000000000073</v>
+      </c>
+      <c r="AK18" s="103">
+        <v>4977.5000000000073</v>
+      </c>
+      <c r="AL18" s="103">
+        <v>312</v>
+      </c>
+      <c r="AM18" s="7"/>
+      <c r="AO18" s="55"/>
+      <c r="AP18" s="105" t="str">
+        <v>Life expectancy of early detection in primary care (6.3, 7.7)</v>
+      </c>
+      <c r="AQ18" s="103">
+        <v>-73300.000000001557</v>
+      </c>
+      <c r="AR18" s="103">
+        <v>660.36036036035966</v>
+      </c>
+      <c r="AS18" s="103">
+        <v>73960.360360361912</v>
+      </c>
+      <c r="AT18" s="103">
+        <v>-466.49999999999784</v>
+      </c>
+      <c r="AU18" s="103">
+        <v>10733.500000000013</v>
+      </c>
+      <c r="AV18" s="103">
+        <v>11200.000000000011</v>
+      </c>
+      <c r="AW18" s="42"/>
+    </row>
+    <row r="19" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="6"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="82" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="83">
+        <v>0.1</v>
+      </c>
+      <c r="J19" s="183" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" s="183"/>
+      <c r="L19" s="183"/>
+      <c r="M19" s="183"/>
+      <c r="N19" s="30"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="169" t="s">
+        <v>7</v>
+      </c>
+      <c r="U19" s="170"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="142"/>
+      <c r="Z19" s="104"/>
+      <c r="AA19" s="78"/>
+      <c r="AB19" s="143"/>
+      <c r="AC19" s="7"/>
+      <c r="AE19" s="6"/>
+      <c r="AF19" s="100" t="str">
+        <v>Cost of early detection in routine practice (2,727., 3,333.)</v>
+      </c>
+      <c r="AG19" s="101">
+        <v>1718.3636363636315</v>
+      </c>
+      <c r="AH19" s="101">
+        <v>947.09090909091049</v>
+      </c>
+      <c r="AI19" s="101">
+        <v>771.272727272721</v>
+      </c>
+      <c r="AJ19" s="101">
+        <v>5027.450000000008</v>
+      </c>
+      <c r="AK19" s="101">
+        <v>5239.5500000000065</v>
+      </c>
+      <c r="AL19" s="101">
+        <v>212.09999999999854</v>
+      </c>
+      <c r="AM19" s="7"/>
+      <c r="AO19" s="55"/>
+      <c r="AP19" s="105" t="str">
+        <v>Life expectancy of early detection in routine practice (6.3, 7.7)</v>
+      </c>
+      <c r="AQ19" s="103">
+        <v>704.8076923076917</v>
+      </c>
+      <c r="AR19" s="103">
+        <v>12216.666666666746</v>
+      </c>
+      <c r="AS19" s="103">
+        <v>11511.858974359055</v>
+      </c>
+      <c r="AT19" s="103">
+        <v>10033.500000000009</v>
+      </c>
+      <c r="AU19" s="103">
+        <v>233.49999999999613</v>
+      </c>
+      <c r="AV19" s="103">
+        <v>9800.0000000000127</v>
+      </c>
+      <c r="AW19" s="42"/>
+    </row>
+    <row r="20" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="6"/>
+      <c r="D20" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="124" t="s">
+        <v>60</v>
+      </c>
+      <c r="K20" s="147" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="147" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" s="148" t="s">
+        <v>63</v>
+      </c>
+      <c r="N20" s="7"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="142"/>
+      <c r="Z20" s="104"/>
+      <c r="AA20" s="140"/>
+      <c r="AB20" s="143"/>
+      <c r="AC20" s="7"/>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="61"/>
+      <c r="AG20" s="61"/>
+      <c r="AH20" s="61"/>
+      <c r="AI20" s="61"/>
+      <c r="AJ20" s="61"/>
+      <c r="AK20" s="61"/>
+      <c r="AL20" s="61"/>
+      <c r="AM20" s="7"/>
+      <c r="AO20" s="55"/>
+      <c r="AP20" s="105" t="str">
+        <v>Probability of early detection in primary care (0.36, 0.44)</v>
+      </c>
+      <c r="AQ20" s="103">
+        <v>13136.363636363492</v>
+      </c>
+      <c r="AR20" s="103">
+        <v>21.21212121212119</v>
+      </c>
+      <c r="AS20" s="103">
+        <v>13115.15151515137</v>
+      </c>
+      <c r="AT20" s="103">
+        <v>377.50000000001205</v>
+      </c>
+      <c r="AU20" s="103">
+        <v>9889.5000000000109</v>
+      </c>
+      <c r="AV20" s="103">
+        <v>9511.9999999999982</v>
+      </c>
+      <c r="AW20" s="42"/>
+    </row>
+    <row r="21" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="6"/>
+      <c r="D21" s="181" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="31">
+        <v>0.35</v>
+      </c>
+      <c r="H21" s="32">
+        <f t="shared" ref="H21:H35" si="0">G21*(1-$I$19)</f>
+        <v>0.315</v>
+      </c>
+      <c r="I21" s="57">
+        <f t="shared" ref="I21:I35" si="1">G21*(1+$I$19)</f>
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="J21" s="127">
+        <v>1</v>
+      </c>
+      <c r="K21" s="149">
+        <f>IF(J21=1,COUNTIF($J$21:J21,1)*2-1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="L21" s="149">
+        <f>IF(J21=1,COUNTIF($J$21:J21,1)*2,"")</f>
+        <v>2</v>
+      </c>
+      <c r="M21" s="150">
+        <f t="shared" ref="M21:M35" si="2">IF(ID=K21,H21,IF(ID=L21,I21,G21))</f>
+        <v>0.35</v>
+      </c>
+      <c r="N21" s="7"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13"/>
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="142"/>
+      <c r="Z21" s="104"/>
+      <c r="AA21" s="140"/>
+      <c r="AB21" s="143"/>
+      <c r="AC21" s="7"/>
+      <c r="AE21" s="6"/>
+      <c r="AF21" s="61"/>
+      <c r="AG21" s="61"/>
+      <c r="AH21" s="61"/>
+      <c r="AI21" s="61"/>
+      <c r="AJ21" s="61"/>
+      <c r="AK21" s="61"/>
+      <c r="AL21" s="61"/>
+      <c r="AM21" s="7"/>
+      <c r="AO21" s="55"/>
+      <c r="AP21" s="105" t="str">
+        <v>Probability of early detection in routine practice (0.315, 0.385)</v>
+      </c>
+      <c r="AQ21" s="103">
+        <v>110.90909090908774</v>
+      </c>
+      <c r="AR21" s="103">
+        <v>8256.3636363636306</v>
+      </c>
+      <c r="AS21" s="103">
+        <v>8145.4545454545432</v>
+      </c>
+      <c r="AT21" s="103">
+        <v>9298.1500000000069</v>
+      </c>
+      <c r="AU21" s="103">
+        <v>968.85000000000082</v>
+      </c>
+      <c r="AV21" s="103">
+        <v>8329.3000000000065</v>
+      </c>
+      <c r="AW21" s="42"/>
+    </row>
+    <row r="22" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="6"/>
+      <c r="D22" s="182"/>
+      <c r="E22" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="33">
+        <v>0.4</v>
+      </c>
+      <c r="H22" s="34">
+        <f t="shared" si="0"/>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="I22" s="58">
+        <f t="shared" si="1"/>
+        <v>0.44000000000000006</v>
+      </c>
+      <c r="J22" s="129">
+        <v>1</v>
+      </c>
+      <c r="K22" s="151">
+        <f>IF(J22=1,COUNTIF($J$21:J22,1)*2-1,"")</f>
+        <v>3</v>
+      </c>
+      <c r="L22" s="151">
+        <f>IF(J22=1,COUNTIF($J$21:J22,1)*2,"")</f>
+        <v>4</v>
+      </c>
+      <c r="M22" s="152">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
+      </c>
+      <c r="N22" s="7"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="170" t="s">
+        <v>6</v>
+      </c>
+      <c r="U22" s="170"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="142"/>
+      <c r="Z22" s="104"/>
+      <c r="AA22" s="78"/>
+      <c r="AB22" s="143"/>
+      <c r="AC22" s="7"/>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="61"/>
+      <c r="AG22" s="61"/>
+      <c r="AH22" s="61"/>
+      <c r="AI22" s="61"/>
+      <c r="AJ22" s="61"/>
+      <c r="AK22" s="61"/>
+      <c r="AL22" s="61"/>
+      <c r="AM22" s="7"/>
+      <c r="AO22" s="55"/>
+      <c r="AP22" s="105" t="str">
+        <v>Life expectancy of late detection in routine practice (1.35, 1.65)</v>
+      </c>
+      <c r="AQ22" s="103">
+        <v>983.89261744966313</v>
+      </c>
+      <c r="AR22" s="103">
+        <v>2064.7887323943637</v>
+      </c>
+      <c r="AS22" s="103">
+        <v>1080.8961149447005</v>
+      </c>
+      <c r="AT22" s="103">
+        <v>7083.50000000001</v>
+      </c>
+      <c r="AU22" s="103">
+        <v>3183.5000000000041</v>
+      </c>
+      <c r="AV22" s="103">
+        <v>3900.0000000000059</v>
+      </c>
+      <c r="AW22" s="42"/>
+    </row>
+    <row r="23" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="6"/>
+      <c r="D23" s="182"/>
+      <c r="E23" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="H23" s="34">
+        <f t="shared" si="0"/>
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="I23" s="58">
+        <f t="shared" si="1"/>
+        <v>0.49500000000000005</v>
+      </c>
+      <c r="J23" s="129">
+        <v>1</v>
+      </c>
+      <c r="K23" s="151">
+        <f>IF(J23=1,COUNTIF($J$21:J23,1)*2-1,"")</f>
+        <v>5</v>
+      </c>
+      <c r="L23" s="151">
+        <f>IF(J23=1,COUNTIF($J$21:J23,1)*2,"")</f>
+        <v>6</v>
+      </c>
+      <c r="M23" s="152">
+        <f t="shared" si="2"/>
+        <v>0.45</v>
+      </c>
+      <c r="N23" s="7"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="21"/>
+      <c r="T23" s="13"/>
+      <c r="U23" s="13"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="142"/>
+      <c r="Z23" s="104"/>
+      <c r="AA23" s="140"/>
+      <c r="AB23" s="143"/>
+      <c r="AC23" s="7"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="61"/>
+      <c r="AG23" s="61"/>
+      <c r="AH23" s="61"/>
+      <c r="AI23" s="61"/>
+      <c r="AJ23" s="61"/>
+      <c r="AK23" s="104"/>
+      <c r="AL23" s="61"/>
+      <c r="AM23" s="7"/>
+      <c r="AO23" s="55"/>
+      <c r="AP23" s="105" t="str">
+        <v>Life expectancy of late detection in primary care (1.35, 1.65)</v>
+      </c>
+      <c r="AQ23" s="103">
+        <v>1981.0810810810758</v>
+      </c>
+      <c r="AR23" s="103">
+        <v>1004.1095890410953</v>
+      </c>
+      <c r="AS23" s="103">
+        <v>976.97149203998049</v>
+      </c>
+      <c r="AT23" s="103">
+        <v>3333.50000000001</v>
+      </c>
+      <c r="AU23" s="103">
+        <v>6933.5000000000045</v>
+      </c>
+      <c r="AV23" s="103">
+        <v>3599.9999999999945</v>
+      </c>
+      <c r="AW23" s="42"/>
+    </row>
+    <row r="24" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="6"/>
+      <c r="D24" s="167" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="72">
+        <v>3030</v>
+      </c>
+      <c r="H24" s="72">
+        <f t="shared" si="0"/>
+        <v>2727</v>
+      </c>
+      <c r="I24" s="73">
+        <f t="shared" si="1"/>
+        <v>3333.0000000000005</v>
+      </c>
+      <c r="J24" s="131">
+        <v>1</v>
+      </c>
+      <c r="K24" s="151">
+        <f>IF(J24=1,COUNTIF($J$21:J24,1)*2-1,"")</f>
+        <v>7</v>
+      </c>
+      <c r="L24" s="151">
+        <f>IF(J24=1,COUNTIF($J$21:J24,1)*2,"")</f>
+        <v>8</v>
+      </c>
+      <c r="M24" s="153">
+        <f t="shared" si="2"/>
+        <v>3030</v>
+      </c>
+      <c r="N24" s="7"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="19"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="142"/>
+      <c r="Z24" s="104"/>
+      <c r="AA24" s="140"/>
+      <c r="AB24" s="143"/>
+      <c r="AC24" s="7"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="61"/>
+      <c r="AG24" s="61"/>
+      <c r="AH24" s="61"/>
+      <c r="AI24" s="61"/>
+      <c r="AJ24" s="61"/>
+      <c r="AK24" s="61"/>
+      <c r="AL24" s="61"/>
+      <c r="AM24" s="7"/>
+      <c r="AO24" s="55"/>
+      <c r="AP24" s="105" t="str">
+        <v>Cost of late detection in routine practice (10,818., 13,222.)</v>
+      </c>
+      <c r="AQ24" s="103">
+        <v>4173.8181818181774</v>
+      </c>
+      <c r="AR24" s="103">
+        <v>-1508.3636363636383</v>
+      </c>
+      <c r="AS24" s="103">
+        <v>5682.1818181818162</v>
+      </c>
+      <c r="AT24" s="103">
+        <v>4352.2000000000071</v>
+      </c>
+      <c r="AU24" s="103">
+        <v>5914.8000000000084</v>
+      </c>
+      <c r="AV24" s="103">
+        <v>1562.6000000000013</v>
+      </c>
+      <c r="AW24" s="42"/>
+    </row>
+    <row r="25" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="6"/>
+      <c r="D25" s="167"/>
+      <c r="E25" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="72">
+        <v>12020</v>
+      </c>
+      <c r="H25" s="72">
+        <f t="shared" si="0"/>
+        <v>10818</v>
+      </c>
+      <c r="I25" s="73">
+        <f t="shared" si="1"/>
+        <v>13222.000000000002</v>
+      </c>
+      <c r="J25" s="131">
+        <v>1</v>
+      </c>
+      <c r="K25" s="151">
+        <f>IF(J25=1,COUNTIF($J$21:J25,1)*2-1,"")</f>
+        <v>9</v>
+      </c>
+      <c r="L25" s="151">
+        <f>IF(J25=1,COUNTIF($J$21:J25,1)*2,"")</f>
+        <v>10</v>
+      </c>
+      <c r="M25" s="153">
+        <f t="shared" si="2"/>
+        <v>12020</v>
+      </c>
+      <c r="N25" s="7"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="13"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="142"/>
+      <c r="Z25" s="104"/>
+      <c r="AA25" s="140"/>
+      <c r="AB25" s="143"/>
+      <c r="AC25" s="7"/>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="61"/>
+      <c r="AG25" s="61"/>
+      <c r="AH25" s="61"/>
+      <c r="AI25" s="61"/>
+      <c r="AJ25" s="61"/>
+      <c r="AK25" s="61"/>
+      <c r="AL25" s="61"/>
+      <c r="AM25" s="7"/>
+      <c r="AO25" s="55"/>
+      <c r="AP25" s="105" t="str">
+        <v>Cost of late detection in primary care (11,520., 14,080.)</v>
+      </c>
+      <c r="AQ25" s="103">
+        <v>-1459.9999999999982</v>
+      </c>
+      <c r="AR25" s="103">
+        <v>4125.4545454545405</v>
+      </c>
+      <c r="AS25" s="103">
+        <v>5585.4545454545387</v>
+      </c>
+      <c r="AT25" s="103">
+        <v>5901.5000000000073</v>
+      </c>
+      <c r="AU25" s="103">
+        <v>4365.5000000000073</v>
+      </c>
+      <c r="AV25" s="103">
+        <v>1536</v>
+      </c>
+      <c r="AW25" s="42"/>
+    </row>
+    <row r="26" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="6"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="72">
+        <v>3900</v>
+      </c>
+      <c r="H26" s="72">
+        <f t="shared" si="0"/>
+        <v>3510</v>
+      </c>
+      <c r="I26" s="73">
+        <f t="shared" si="1"/>
+        <v>4290</v>
+      </c>
+      <c r="J26" s="131">
+        <v>1</v>
+      </c>
+      <c r="K26" s="151">
+        <f>IF(J26=1,COUNTIF($J$21:J26,1)*2-1,"")</f>
+        <v>11</v>
+      </c>
+      <c r="L26" s="151">
+        <f>IF(J26=1,COUNTIF($J$21:J26,1)*2,"")</f>
+        <v>12</v>
+      </c>
+      <c r="M26" s="153">
+        <f t="shared" si="2"/>
+        <v>3900</v>
+      </c>
+      <c r="N26" s="7"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="169" t="s">
+        <v>7</v>
+      </c>
+      <c r="U26" s="170"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="142"/>
+      <c r="Z26" s="104"/>
+      <c r="AA26" s="78"/>
+      <c r="AB26" s="143"/>
+      <c r="AC26" s="7"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="61"/>
+      <c r="AG26" s="61"/>
+      <c r="AH26" s="61"/>
+      <c r="AI26" s="61"/>
+      <c r="AJ26" s="61"/>
+      <c r="AK26" s="110" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL26" s="111">
+        <f>W32</f>
+        <v>5133.5000000000073</v>
+      </c>
+      <c r="AM26" s="7"/>
+      <c r="AO26" s="55"/>
+      <c r="AP26" s="105" t="str">
+        <v>Cost of early detection in primary care (3,510., 4,290.)</v>
+      </c>
+      <c r="AQ26" s="103">
+        <v>765.45454545454447</v>
+      </c>
+      <c r="AR26" s="103">
+        <v>1899.9999999999975</v>
+      </c>
+      <c r="AS26" s="103">
+        <v>1134.5454545454531</v>
+      </c>
+      <c r="AT26" s="103">
+        <v>5289.5000000000073</v>
+      </c>
+      <c r="AU26" s="103">
+        <v>4977.5000000000073</v>
+      </c>
+      <c r="AV26" s="103">
+        <v>312</v>
+      </c>
+      <c r="AW26" s="42"/>
+    </row>
+    <row r="27" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="6"/>
+      <c r="D27" s="167"/>
+      <c r="E27" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="72">
+        <v>12800</v>
+      </c>
+      <c r="H27" s="72">
+        <f t="shared" si="0"/>
+        <v>11520</v>
+      </c>
+      <c r="I27" s="73">
+        <f t="shared" si="1"/>
+        <v>14080.000000000002</v>
+      </c>
+      <c r="J27" s="131">
+        <v>1</v>
+      </c>
+      <c r="K27" s="151">
+        <f>IF(J27=1,COUNTIF($J$21:J27,1)*2-1,"")</f>
+        <v>13</v>
+      </c>
+      <c r="L27" s="151">
+        <f>IF(J27=1,COUNTIF($J$21:J27,1)*2,"")</f>
+        <v>14</v>
+      </c>
+      <c r="M27" s="153">
+        <f t="shared" si="2"/>
+        <v>12800</v>
+      </c>
+      <c r="N27" s="7"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="42"/>
+      <c r="AE27" s="55"/>
+      <c r="AF27" s="61"/>
+      <c r="AG27" s="61"/>
+      <c r="AH27" s="61"/>
+      <c r="AI27" s="61"/>
+      <c r="AJ27" s="61"/>
+      <c r="AK27" s="61"/>
+      <c r="AL27" s="61"/>
+      <c r="AM27" s="42"/>
+      <c r="AO27" s="55"/>
+      <c r="AP27" s="100" t="str">
+        <v>Cost of early detection in routine practice (2,727., 3,333.)</v>
+      </c>
+      <c r="AQ27" s="101">
+        <v>1718.3636363636315</v>
+      </c>
+      <c r="AR27" s="101">
+        <v>947.09090909091049</v>
+      </c>
+      <c r="AS27" s="101">
+        <v>771.272727272721</v>
+      </c>
+      <c r="AT27" s="101">
+        <v>5027.450000000008</v>
+      </c>
+      <c r="AU27" s="101">
+        <v>5239.5500000000065</v>
+      </c>
+      <c r="AV27" s="101">
+        <v>212.09999999999854</v>
+      </c>
+      <c r="AW27" s="42"/>
+    </row>
+    <row r="28" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C28" s="6"/>
+      <c r="D28" s="167"/>
+      <c r="E28" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="72">
+        <v>6200</v>
+      </c>
+      <c r="H28" s="72">
+        <f t="shared" si="0"/>
+        <v>5580</v>
+      </c>
+      <c r="I28" s="73">
+        <f t="shared" si="1"/>
+        <v>6820.0000000000009</v>
+      </c>
+      <c r="J28" s="131">
+        <v>1</v>
+      </c>
+      <c r="K28" s="151">
+        <f>IF(J28=1,COUNTIF($J$21:J28,1)*2-1,"")</f>
+        <v>15</v>
+      </c>
+      <c r="L28" s="151">
+        <f>IF(J28=1,COUNTIF($J$21:J28,1)*2,"")</f>
+        <v>16</v>
+      </c>
+      <c r="M28" s="153">
+        <f t="shared" si="2"/>
+        <v>6200</v>
+      </c>
+      <c r="N28" s="7"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="89" t="s">
+        <v>74</v>
+      </c>
+      <c r="W28" s="90">
+        <v>20000</v>
+      </c>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="42"/>
+      <c r="AE28" s="55"/>
+      <c r="AF28" s="61"/>
+      <c r="AG28" s="61"/>
+      <c r="AH28" s="61"/>
+      <c r="AI28" s="61"/>
+      <c r="AJ28" s="61"/>
+      <c r="AK28" s="61"/>
+      <c r="AL28" s="61"/>
+      <c r="AM28" s="42"/>
+      <c r="AO28" s="55"/>
+      <c r="AP28" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AQ28" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AR28" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AS28" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AT28" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AU28" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AV28" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AW28" s="42"/>
+    </row>
+    <row r="29" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="6"/>
+      <c r="D29" s="167"/>
+      <c r="E29" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="72">
+        <v>14400</v>
+      </c>
+      <c r="H29" s="72">
+        <f t="shared" si="0"/>
+        <v>12960</v>
+      </c>
+      <c r="I29" s="73">
+        <f t="shared" si="1"/>
+        <v>15840.000000000002</v>
+      </c>
+      <c r="J29" s="131">
+        <v>1</v>
+      </c>
+      <c r="K29" s="151">
+        <f>IF(J29=1,COUNTIF($J$21:J29,1)*2-1,"")</f>
+        <v>17</v>
+      </c>
+      <c r="L29" s="151">
+        <f>IF(J29=1,COUNTIF($J$21:J29,1)*2,"")</f>
+        <v>18</v>
+      </c>
+      <c r="M29" s="153">
+        <f t="shared" si="2"/>
+        <v>14400</v>
+      </c>
+      <c r="N29" s="7"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="14"/>
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="42"/>
+      <c r="AE29" s="55"/>
+      <c r="AF29" s="61"/>
+      <c r="AG29" s="61"/>
+      <c r="AH29" s="61"/>
+      <c r="AI29" s="61"/>
+      <c r="AJ29" s="61"/>
+      <c r="AK29" s="104"/>
+      <c r="AL29" s="61"/>
+      <c r="AM29" s="42"/>
+      <c r="AO29" s="55"/>
+      <c r="AP29" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AQ29" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AR29" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AS29" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AT29" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AU29" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AV29" s="14" t="str">
+        <v/>
+      </c>
+      <c r="AW29" s="42"/>
+    </row>
+    <row r="30" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C30" s="6"/>
+      <c r="D30" s="168" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="40">
+        <v>7</v>
+      </c>
+      <c r="H30" s="38">
+        <f t="shared" si="0"/>
+        <v>6.3</v>
+      </c>
+      <c r="I30" s="59">
+        <f t="shared" si="1"/>
+        <v>7.7000000000000011</v>
+      </c>
+      <c r="J30" s="133">
+        <v>1</v>
+      </c>
+      <c r="K30" s="151">
+        <f>IF(J30=1,COUNTIF($J$21:J30,1)*2-1,"")</f>
+        <v>19</v>
+      </c>
+      <c r="L30" s="151">
+        <f>IF(J30=1,COUNTIF($J$21:J30,1)*2,"")</f>
+        <v>20</v>
+      </c>
+      <c r="M30" s="154">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="N30" s="7"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="87"/>
+      <c r="R30" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="S30" s="88" t="s">
+        <v>54</v>
+      </c>
+      <c r="T30" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="U30" s="88" t="s">
+        <v>52</v>
+      </c>
+      <c r="V30" s="88" t="s">
+        <v>53</v>
+      </c>
+      <c r="W30" s="88" t="s">
+        <v>75</v>
+      </c>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+      <c r="AC30" s="42"/>
+      <c r="AE30" s="55"/>
+      <c r="AF30" s="61"/>
+      <c r="AG30" s="61"/>
+      <c r="AH30" s="61"/>
+      <c r="AI30" s="61"/>
+      <c r="AJ30" s="61"/>
+      <c r="AK30" s="61"/>
+      <c r="AL30" s="61"/>
+      <c r="AM30" s="42"/>
+      <c r="AO30" s="55"/>
+      <c r="AP30" s="159" t="str">
+        <v>Hospital Care vs Primary Care</v>
+      </c>
+      <c r="AQ30" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AR30" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AS30" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AT30" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AU30" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AV30" s="159" t="str">
+        <v/>
+      </c>
+      <c r="AW30" s="42"/>
+    </row>
+    <row r="31" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="6"/>
+      <c r="D31" s="168"/>
+      <c r="E31" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" s="40">
+        <v>1.5</v>
+      </c>
+      <c r="H31" s="38">
+        <f t="shared" si="0"/>
+        <v>1.35</v>
+      </c>
+      <c r="I31" s="59">
+        <f t="shared" si="1"/>
+        <v>1.6500000000000001</v>
+      </c>
+      <c r="J31" s="133">
+        <v>1</v>
+      </c>
+      <c r="K31" s="151">
+        <f>IF(J31=1,COUNTIF($J$21:J31,1)*2-1,"")</f>
+        <v>21</v>
+      </c>
+      <c r="L31" s="151">
+        <f>IF(J31=1,COUNTIF($J$21:J31,1)*2,"")</f>
+        <v>22</v>
+      </c>
+      <c r="M31" s="154">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="N31" s="7"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="R31" s="70" cm="1">
+        <f t="array" ref="R31:W33">Tree(G21:G35)</f>
+        <v>8873.5</v>
+      </c>
+      <c r="S31" s="52">
+        <v>3.4249999999999998</v>
+      </c>
+      <c r="T31" s="144">
+        <v>0</v>
+      </c>
+      <c r="U31" s="145">
+        <v>0</v>
+      </c>
+      <c r="V31" s="145">
+        <v>0</v>
+      </c>
+      <c r="W31" s="146">
+        <v>0</v>
+      </c>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="42"/>
+      <c r="AE31" s="55"/>
+      <c r="AF31" s="61"/>
+      <c r="AG31" s="61"/>
+      <c r="AH31" s="61"/>
+      <c r="AI31" s="61"/>
+      <c r="AJ31" s="61"/>
+      <c r="AK31" s="61"/>
+      <c r="AL31" s="61"/>
+      <c r="AM31" s="42"/>
+      <c r="AO31" s="55"/>
+      <c r="AP31" s="84" t="str">
+        <v>Parameter</v>
+      </c>
+      <c r="AQ31" s="84" t="str">
+        <v>ICER LL</v>
+      </c>
+      <c r="AR31" s="84" t="str">
+        <v>ICER UL</v>
+      </c>
+      <c r="AS31" s="84" t="str">
+        <v>ABS ICER</v>
+      </c>
+      <c r="AT31" s="84" t="str">
+        <v>INMB LL</v>
+      </c>
+      <c r="AU31" s="84" t="str">
+        <v>INMB UL</v>
+      </c>
+      <c r="AV31" s="84" t="str">
+        <v>ABS INMB</v>
+      </c>
+      <c r="AW31" s="42"/>
+    </row>
+    <row r="32" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="6"/>
+      <c r="D32" s="168"/>
+      <c r="E32" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="40">
+        <v>7</v>
+      </c>
+      <c r="H32" s="38">
+        <f t="shared" si="0"/>
+        <v>6.3</v>
+      </c>
+      <c r="I32" s="59">
+        <f t="shared" si="1"/>
+        <v>7.7000000000000011</v>
+      </c>
+      <c r="J32" s="133">
+        <v>1</v>
+      </c>
+      <c r="K32" s="151">
+        <f>IF(J32=1,COUNTIF($J$21:J32,1)*2-1,"")</f>
+        <v>23</v>
+      </c>
+      <c r="L32" s="151">
+        <f>IF(J32=1,COUNTIF($J$21:J32,1)*2,"")</f>
+        <v>24</v>
+      </c>
+      <c r="M32" s="154">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="N32" s="7"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="70">
+        <v>9240</v>
+      </c>
+      <c r="S32" s="52">
+        <v>3.7</v>
+      </c>
+      <c r="T32" s="70">
+        <v>366.5</v>
+      </c>
+      <c r="U32" s="34">
+        <v>0.27500000000000036</v>
+      </c>
+      <c r="V32" s="118">
+        <v>1332.7272727272709</v>
+      </c>
+      <c r="W32" s="118">
+        <v>5133.5000000000073</v>
+      </c>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="42"/>
+      <c r="AE32" s="55"/>
+      <c r="AF32" s="61"/>
+      <c r="AG32" s="61"/>
+      <c r="AH32" s="61"/>
+      <c r="AI32" s="61"/>
+      <c r="AJ32" s="61"/>
+      <c r="AK32" s="61"/>
+      <c r="AL32" s="61"/>
+      <c r="AM32" s="42"/>
+      <c r="AO32" s="55"/>
+      <c r="AP32" s="105" t="str">
+        <v>Life expectancy of early detection in hospital care (6.3, 7.7)</v>
+      </c>
+      <c r="AQ32" s="103">
+        <v>-36749.999999999971</v>
+      </c>
+      <c r="AR32" s="103">
+        <v>2491.5254237288104</v>
+      </c>
+      <c r="AS32" s="103">
+        <v>39241.525423728781</v>
+      </c>
+      <c r="AT32" s="103">
+        <v>-2270.0000000000009</v>
+      </c>
+      <c r="AU32" s="103">
+        <v>10330.000000000015</v>
+      </c>
+      <c r="AV32" s="103">
+        <v>12600.000000000015</v>
+      </c>
+      <c r="AW32" s="42"/>
+    </row>
+    <row r="33" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="6"/>
+      <c r="D33" s="168"/>
+      <c r="E33" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="40">
+        <v>1.5</v>
+      </c>
+      <c r="H33" s="38">
+        <f t="shared" si="0"/>
+        <v>1.35</v>
+      </c>
+      <c r="I33" s="59">
+        <f t="shared" si="1"/>
+        <v>1.6500000000000001</v>
+      </c>
+      <c r="J33" s="133">
+        <v>1</v>
+      </c>
+      <c r="K33" s="151">
+        <f>IF(J33=1,COUNTIF($J$21:J33,1)*2-1,"")</f>
+        <v>25</v>
+      </c>
+      <c r="L33" s="151">
+        <f>IF(J33=1,COUNTIF($J$21:J33,1)*2,"")</f>
+        <v>26</v>
+      </c>
+      <c r="M33" s="154">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="N33" s="7"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="70">
+        <v>10710</v>
+      </c>
+      <c r="S33" s="52">
+        <v>3.9750000000000001</v>
+      </c>
+      <c r="T33" s="70">
+        <v>1470</v>
+      </c>
+      <c r="U33" s="52">
+        <v>0.27499999999999991</v>
+      </c>
+      <c r="V33" s="118">
+        <v>5345.4545454545469</v>
+      </c>
+      <c r="W33" s="118">
+        <v>4029.9999999999982</v>
+      </c>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="42"/>
+      <c r="AE33" s="55"/>
+      <c r="AF33" s="61"/>
+      <c r="AG33" s="61"/>
+      <c r="AH33" s="61"/>
+      <c r="AI33" s="61"/>
+      <c r="AJ33" s="61"/>
+      <c r="AK33" s="61"/>
+      <c r="AL33" s="61"/>
+      <c r="AM33" s="42"/>
+      <c r="AO33" s="55"/>
+      <c r="AP33" s="105" t="str">
+        <v>Life expectancy of early detection in primary care (6.3, 7.7)</v>
+      </c>
+      <c r="AQ33" s="103">
+        <v>2648.6486486486478</v>
+      </c>
+      <c r="AR33" s="103">
+        <v>-293999.99999998015</v>
+      </c>
+      <c r="AS33" s="103">
+        <v>296648.64864862879</v>
+      </c>
+      <c r="AT33" s="103">
+        <v>9630.0000000000036</v>
+      </c>
+      <c r="AU33" s="103">
+        <v>-1570.0000000000068</v>
+      </c>
+      <c r="AV33" s="103">
+        <v>11200.000000000011</v>
+      </c>
+      <c r="AW33" s="42"/>
+    </row>
+    <row r="34" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="6"/>
+      <c r="D34" s="168"/>
+      <c r="E34" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" s="40">
+        <v>7</v>
+      </c>
+      <c r="H34" s="38">
+        <f t="shared" si="0"/>
+        <v>6.3</v>
+      </c>
+      <c r="I34" s="59">
+        <f t="shared" si="1"/>
+        <v>7.7000000000000011</v>
+      </c>
+      <c r="J34" s="133">
+        <v>1</v>
+      </c>
+      <c r="K34" s="151">
+        <f>IF(J34=1,COUNTIF($J$21:J34,1)*2-1,"")</f>
+        <v>27</v>
+      </c>
+      <c r="L34" s="151">
+        <f>IF(J34=1,COUNTIF($J$21:J34,1)*2,"")</f>
+        <v>28</v>
+      </c>
+      <c r="M34" s="154">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="N34" s="7"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="14"/>
+      <c r="Y34" s="14"/>
+      <c r="Z34" s="14"/>
+      <c r="AA34" s="14"/>
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="42"/>
+      <c r="AE34" s="55"/>
+      <c r="AF34" s="159" t="str">
+        <f>Q33&amp;" vs "&amp;Q32</f>
+        <v>Hospital Care vs Primary Care</v>
+      </c>
+      <c r="AG34" s="159"/>
+      <c r="AH34" s="159"/>
+      <c r="AI34" s="159"/>
+      <c r="AJ34" s="159"/>
+      <c r="AK34" s="159"/>
+      <c r="AL34" s="159"/>
+      <c r="AM34" s="42"/>
+      <c r="AO34" s="55"/>
+      <c r="AP34" s="105" t="str">
+        <v>Probability of early detection in hospital care (0.405, 0.495)</v>
+      </c>
+      <c r="AQ34" s="103">
+        <v>66872.727272727614</v>
+      </c>
+      <c r="AR34" s="103">
+        <v>2107.1770334928196</v>
+      </c>
+      <c r="AS34" s="103">
+        <v>64765.550239234792</v>
+      </c>
+      <c r="AT34" s="103">
+        <v>-1289.0000000000027</v>
+      </c>
+      <c r="AU34" s="103">
+        <v>9349.0000000000018</v>
+      </c>
+      <c r="AV34" s="103">
+        <v>10638.000000000004</v>
+      </c>
+      <c r="AW34" s="42"/>
+    </row>
+    <row r="35" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="6"/>
+      <c r="D35" s="168"/>
+      <c r="E35" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="40">
+        <v>1.5</v>
+      </c>
+      <c r="H35" s="38">
+        <f t="shared" si="0"/>
+        <v>1.35</v>
+      </c>
+      <c r="I35" s="59">
+        <f t="shared" si="1"/>
+        <v>1.6500000000000001</v>
+      </c>
+      <c r="J35" s="135">
+        <v>1</v>
+      </c>
+      <c r="K35" s="155">
+        <f>IF(J35=1,COUNTIF($J$21:J35,1)*2-1,"")</f>
+        <v>29</v>
+      </c>
+      <c r="L35" s="155">
+        <f>IF(J35=1,COUNTIF($J$21:J35,1)*2,"")</f>
+        <v>30</v>
+      </c>
+      <c r="M35" s="156">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="N35" s="7"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="14"/>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14"/>
+      <c r="S35" s="14"/>
+      <c r="T35" s="14"/>
+      <c r="U35" s="14"/>
+      <c r="V35" s="14"/>
+      <c r="W35" s="14"/>
+      <c r="X35" s="14"/>
+      <c r="Y35" s="14"/>
+      <c r="Z35" s="14"/>
+      <c r="AA35" s="14"/>
+      <c r="AB35" s="14"/>
+      <c r="AC35" s="42"/>
+      <c r="AE35" s="55"/>
+      <c r="AF35" s="84" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG35" s="84" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH35" s="84" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI35" s="84" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ35" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK35" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL35" s="84" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM35" s="42"/>
+      <c r="AO35" s="55"/>
+      <c r="AP35" s="105" t="str">
+        <v>Probability of early detection in primary care (0.36, 0.44)</v>
+      </c>
+      <c r="AQ35" s="103">
+        <v>2250.5050505050522</v>
+      </c>
+      <c r="AR35" s="103">
+        <v>33200.000000000175</v>
+      </c>
+      <c r="AS35" s="103">
+        <v>30949.494949495122</v>
+      </c>
+      <c r="AT35" s="103">
+        <v>8785.9999999999927</v>
+      </c>
+      <c r="AU35" s="103">
+        <v>-726.00000000000568</v>
+      </c>
+      <c r="AV35" s="103">
+        <v>9511.9999999999982</v>
+      </c>
+      <c r="AW35" s="42"/>
+    </row>
+    <row r="36" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="8"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="10"/>
+      <c r="P36" s="8"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="10"/>
+      <c r="AE36" s="55"/>
+      <c r="AF36" s="105" t="str" cm="1">
+        <f t="array" ref="AF36:AL45">_xlfn.LET(
+    _xlpm.names,$F$21:$F$35,
+    _xlpm.desc,$E$21:$E$35,
+    _xlpm.base,$G$21:$G$35,
+    _xlpm.low,$H$21:$H$35,
+    _xlpm.high,$I$21:$I$35,
+    _xlpm.inc,$J$21:$J$35,
+    _xlpm.idx,_xlfn.SEQUENCE(ROWS(_xlpm.base)),
+    _xlpm.label,_xlpm.desc&amp;" ("&amp;TEXT(_xlpm.low,"#,##0.###")&amp;", "&amp;TEXT(_xlpm.high,"#,##0.###")&amp;")",
+    _xlpm.llI,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+        INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.low,_xlpm.i),_xlpm.base)),3,5)
+    )),
+    _xlpm.ulI,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+        INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.high,_xlpm.i),_xlpm.base)),3,5)
+    )),
+    _xlpm.llN,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+        INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.low,_xlpm.i),_xlpm.base)),3,6)
+    )),
+    _xlpm.ulN,_xlfn.MAP(_xlpm.idx,_xlfn.LAMBDA(_xlpm.i,
+        INDEX(Tree(IF(_xlpm.idx=_xlpm.i,INDEX(_xlpm.high,_xlpm.i),_xlpm.base)),3,6)
+    )),
+    _xlpm.data,_xlfn.HSTACK(
+        _xlpm.label,_xlpm.llI,_xlpm.ulI,ABS(_xlpm.ulI-_xlpm.llI),
+        _xlpm.llN,_xlpm.ulN,ABS(_xlpm.ulN-_xlpm.llN)
+    ),
+    _xlpm.result,_xlfn._xlws.FILTER(_xlpm.data,(_xlpm.inc=1)*(LEFT(_xlpm.names,2)&lt;&gt;"RP")),
+    _xlfn.SORTBY(_xlpm.result,_xlfn.CHOOSECOLS(_xlpm.result,7),-1)
+)</f>
+        <v>Life expectancy of early detection in hospital care (6.3, 7.7)</v>
+      </c>
+      <c r="AG36" s="103">
+        <v>-36749.999999999971</v>
+      </c>
+      <c r="AH36" s="103">
+        <v>2491.5254237288104</v>
+      </c>
+      <c r="AI36" s="103">
+        <v>39241.525423728781</v>
+      </c>
+      <c r="AJ36" s="103">
+        <v>-2270.0000000000009</v>
+      </c>
+      <c r="AK36" s="103">
+        <v>10330.000000000015</v>
+      </c>
+      <c r="AL36" s="103">
+        <v>12600.000000000015</v>
+      </c>
+      <c r="AM36" s="42"/>
+      <c r="AO36" s="55"/>
+      <c r="AP36" s="105" t="str">
+        <v>Life expectancy of late detection in primary care (1.35, 1.65)</v>
+      </c>
+      <c r="AQ36" s="103">
+        <v>4027.397260273975</v>
+      </c>
+      <c r="AR36" s="103">
+        <v>7945.945945945944</v>
+      </c>
+      <c r="AS36" s="103">
+        <v>3918.548685671969</v>
+      </c>
+      <c r="AT36" s="103">
+        <v>5829.9999999999955</v>
+      </c>
+      <c r="AU36" s="103">
+        <v>2230.0000000000009</v>
+      </c>
+      <c r="AV36" s="103">
+        <v>3599.9999999999945</v>
+      </c>
+      <c r="AW36" s="42"/>
+    </row>
+    <row r="37" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE37" s="55"/>
+      <c r="AF37" s="105" t="str">
+        <v>Life expectancy of early detection in primary care (6.3, 7.7)</v>
+      </c>
+      <c r="AG37" s="103">
+        <v>2648.6486486486478</v>
+      </c>
+      <c r="AH37" s="103">
+        <v>-293999.99999998015</v>
+      </c>
+      <c r="AI37" s="103">
+        <v>296648.64864862879</v>
+      </c>
+      <c r="AJ37" s="103">
+        <v>9630.0000000000036</v>
+      </c>
+      <c r="AK37" s="103">
+        <v>-1570.0000000000068</v>
+      </c>
+      <c r="AL37" s="103">
+        <v>11200.000000000011</v>
+      </c>
+      <c r="AM37" s="42"/>
+      <c r="AO37" s="55"/>
+      <c r="AP37" s="105" t="str">
+        <v>Life expectancy of late detection in hospital care (1.35, 1.65)</v>
+      </c>
+      <c r="AQ37" s="103">
+        <v>7636.3636363636406</v>
+      </c>
+      <c r="AR37" s="103">
+        <v>4111.8881118881127</v>
+      </c>
+      <c r="AS37" s="103">
+        <v>3524.4755244755279</v>
+      </c>
+      <c r="AT37" s="103">
+        <v>2379.9999999999977</v>
+      </c>
+      <c r="AU37" s="103">
+        <v>5679.9999999999982</v>
+      </c>
+      <c r="AV37" s="103">
+        <v>3300.0000000000005</v>
+      </c>
+      <c r="AW37" s="42"/>
+    </row>
+    <row r="38" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE38" s="55"/>
+      <c r="AF38" s="105" t="str">
+        <v>Probability of early detection in hospital care (0.405, 0.495)</v>
+      </c>
+      <c r="AG38" s="103">
+        <v>66872.727272727614</v>
+      </c>
+      <c r="AH38" s="103">
+        <v>2107.1770334928196</v>
+      </c>
+      <c r="AI38" s="103">
+        <v>64765.550239234792</v>
+      </c>
+      <c r="AJ38" s="103">
+        <v>-1289.0000000000027</v>
+      </c>
+      <c r="AK38" s="103">
+        <v>9349.0000000000018</v>
+      </c>
+      <c r="AL38" s="103">
+        <v>10638.000000000004</v>
+      </c>
+      <c r="AM38" s="42"/>
+      <c r="AO38" s="55"/>
+      <c r="AP38" s="105" t="str">
+        <v>Cost of late detection in hospital care (12,960., 15,840.)</v>
+      </c>
+      <c r="AQ38" s="103">
+        <v>2465.4545454545464</v>
+      </c>
+      <c r="AR38" s="103">
+        <v>8225.454545454555</v>
+      </c>
+      <c r="AS38" s="103">
+        <v>5760.0000000000091</v>
+      </c>
+      <c r="AT38" s="103">
+        <v>4821.9999999999982</v>
+      </c>
+      <c r="AU38" s="103">
+        <v>3237.9999999999964</v>
+      </c>
+      <c r="AV38" s="103">
+        <v>1584.0000000000018</v>
+      </c>
+      <c r="AW38" s="42"/>
+    </row>
+    <row r="39" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE39" s="55"/>
+      <c r="AF39" s="105" t="str">
+        <v>Probability of early detection in primary care (0.36, 0.44)</v>
+      </c>
+      <c r="AG39" s="103">
+        <v>2250.5050505050522</v>
+      </c>
+      <c r="AH39" s="103">
+        <v>33200.000000000175</v>
+      </c>
+      <c r="AI39" s="103">
+        <v>30949.494949495122</v>
+      </c>
+      <c r="AJ39" s="103">
+        <v>8785.9999999999927</v>
+      </c>
+      <c r="AK39" s="103">
+        <v>-726.00000000000568</v>
+      </c>
+      <c r="AL39" s="103">
+        <v>9511.9999999999982</v>
+      </c>
+      <c r="AM39" s="42"/>
+      <c r="AO39" s="55"/>
+      <c r="AP39" s="105" t="str">
+        <v>Cost of late detection in primary care (11,520., 14,080.)</v>
+      </c>
+      <c r="AQ39" s="103">
+        <v>8138.1818181818207</v>
+      </c>
+      <c r="AR39" s="103">
+        <v>2552.7272727272734</v>
+      </c>
+      <c r="AS39" s="103">
+        <v>5585.4545454545478</v>
+      </c>
+      <c r="AT39" s="103">
+        <v>3261.9999999999982</v>
+      </c>
+      <c r="AU39" s="103">
+        <v>4797.9999999999982</v>
+      </c>
+      <c r="AV39" s="103">
+        <v>1536</v>
+      </c>
+      <c r="AW39" s="42"/>
+    </row>
+    <row r="40" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE40" s="55"/>
+      <c r="AF40" s="105" t="str">
+        <v>Life expectancy of late detection in primary care (1.35, 1.65)</v>
+      </c>
+      <c r="AG40" s="103">
+        <v>4027.397260273975</v>
+      </c>
+      <c r="AH40" s="103">
+        <v>7945.945945945944</v>
+      </c>
+      <c r="AI40" s="103">
+        <v>3918.548685671969</v>
+      </c>
+      <c r="AJ40" s="103">
+        <v>5829.9999999999955</v>
+      </c>
+      <c r="AK40" s="103">
+        <v>2230.0000000000009</v>
+      </c>
+      <c r="AL40" s="103">
+        <v>3599.9999999999945</v>
+      </c>
+      <c r="AM40" s="42"/>
+      <c r="AO40" s="55"/>
+      <c r="AP40" s="105" t="str">
+        <v>Cost of early detection in hospital care (5,580., 6,820.)</v>
+      </c>
+      <c r="AQ40" s="103">
+        <v>4330.9090909090919</v>
+      </c>
+      <c r="AR40" s="103">
+        <v>6360.0000000000091</v>
+      </c>
+      <c r="AS40" s="103">
+        <v>2029.0909090909172</v>
+      </c>
+      <c r="AT40" s="103">
+        <v>4308.9999999999982</v>
+      </c>
+      <c r="AU40" s="103">
+        <v>3750.9999999999964</v>
+      </c>
+      <c r="AV40" s="103">
+        <v>558.00000000000182</v>
+      </c>
+      <c r="AW40" s="42"/>
+    </row>
+    <row r="41" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AE41" s="55"/>
+      <c r="AF41" s="105" t="str">
+        <v>Life expectancy of late detection in hospital care (1.35, 1.65)</v>
+      </c>
+      <c r="AG41" s="103">
+        <v>7636.3636363636406</v>
+      </c>
+      <c r="AH41" s="103">
+        <v>4111.8881118881127</v>
+      </c>
+      <c r="AI41" s="103">
+        <v>3524.4755244755279</v>
+      </c>
+      <c r="AJ41" s="103">
+        <v>2379.9999999999977</v>
+      </c>
+      <c r="AK41" s="103">
+        <v>5679.9999999999982</v>
+      </c>
+      <c r="AL41" s="103">
+        <v>3300.0000000000005</v>
+      </c>
+      <c r="AM41" s="42"/>
+      <c r="AO41" s="55"/>
+      <c r="AP41" s="100" t="str">
+        <v>Cost of early detection in primary care (3,510., 4,290.)</v>
+      </c>
+      <c r="AQ41" s="101">
+        <v>5912.7272727272748</v>
+      </c>
+      <c r="AR41" s="101">
+        <v>4778.1818181818198</v>
+      </c>
+      <c r="AS41" s="101">
+        <v>1134.545454545455</v>
+      </c>
+      <c r="AT41" s="101">
+        <v>3873.9999999999982</v>
+      </c>
+      <c r="AU41" s="101">
+        <v>4185.9999999999982</v>
+      </c>
+      <c r="AV41" s="101">
+        <v>312</v>
+      </c>
+      <c r="AW41" s="42"/>
+    </row>
+    <row r="42" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE42" s="55"/>
+      <c r="AF42" s="105" t="str">
+        <v>Cost of late detection in hospital care (12,960., 15,840.)</v>
+      </c>
+      <c r="AG42" s="103">
+        <v>2465.4545454545464</v>
+      </c>
+      <c r="AH42" s="103">
+        <v>8225.454545454555</v>
+      </c>
+      <c r="AI42" s="103">
+        <v>5760.0000000000091</v>
+      </c>
+      <c r="AJ42" s="103">
+        <v>4821.9999999999982</v>
+      </c>
+      <c r="AK42" s="103">
+        <v>3237.9999999999964</v>
+      </c>
+      <c r="AL42" s="103">
+        <v>1584.0000000000018</v>
+      </c>
+      <c r="AM42" s="42"/>
+      <c r="AO42" s="55"/>
+      <c r="AP42" s="14"/>
+      <c r="AQ42" s="14"/>
+      <c r="AR42" s="14"/>
+      <c r="AS42" s="14"/>
+      <c r="AT42" s="14"/>
+      <c r="AU42" s="14"/>
+      <c r="AV42" s="14"/>
+      <c r="AW42" s="42"/>
+    </row>
+    <row r="43" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE43" s="55"/>
+      <c r="AF43" s="105" t="str">
+        <v>Cost of late detection in primary care (11,520., 14,080.)</v>
+      </c>
+      <c r="AG43" s="103">
+        <v>8138.1818181818207</v>
+      </c>
+      <c r="AH43" s="103">
+        <v>2552.7272727272734</v>
+      </c>
+      <c r="AI43" s="103">
+        <v>5585.4545454545478</v>
+      </c>
+      <c r="AJ43" s="103">
+        <v>3261.9999999999982</v>
+      </c>
+      <c r="AK43" s="103">
+        <v>4797.9999999999982</v>
+      </c>
+      <c r="AL43" s="103">
+        <v>1536</v>
+      </c>
+      <c r="AM43" s="42"/>
+      <c r="AO43" s="95"/>
+      <c r="AP43" s="114"/>
+      <c r="AQ43" s="114"/>
+      <c r="AR43" s="114"/>
+      <c r="AS43" s="114"/>
+      <c r="AT43" s="114"/>
+      <c r="AU43" s="114"/>
+      <c r="AV43" s="114"/>
+      <c r="AW43" s="99"/>
+    </row>
+    <row r="44" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE44" s="55"/>
+      <c r="AF44" s="105" t="str">
+        <v>Cost of early detection in hospital care (5,580., 6,820.)</v>
+      </c>
+      <c r="AG44" s="103">
+        <v>4330.9090909090919</v>
+      </c>
+      <c r="AH44" s="103">
+        <v>6360.0000000000091</v>
+      </c>
+      <c r="AI44" s="103">
+        <v>2029.0909090909172</v>
+      </c>
+      <c r="AJ44" s="103">
+        <v>4308.9999999999982</v>
+      </c>
+      <c r="AK44" s="103">
+        <v>3750.9999999999964</v>
+      </c>
+      <c r="AL44" s="103">
+        <v>558.00000000000182</v>
+      </c>
+      <c r="AM44" s="42"/>
+    </row>
+    <row r="45" spans="3:49" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AE45" s="55"/>
+      <c r="AF45" s="100" t="str">
+        <v>Cost of early detection in primary care (3,510., 4,290.)</v>
+      </c>
+      <c r="AG45" s="101">
+        <v>5912.7272727272748</v>
+      </c>
+      <c r="AH45" s="101">
+        <v>4778.1818181818198</v>
+      </c>
+      <c r="AI45" s="101">
+        <v>1134.545454545455</v>
+      </c>
+      <c r="AJ45" s="101">
+        <v>3873.9999999999982</v>
+      </c>
+      <c r="AK45" s="101">
+        <v>4185.9999999999982</v>
+      </c>
+      <c r="AL45" s="101">
+        <v>312</v>
+      </c>
+      <c r="AM45" s="42"/>
+    </row>
+    <row r="46" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE46" s="55"/>
+      <c r="AF46" s="61"/>
+      <c r="AG46" s="61"/>
+      <c r="AH46" s="61"/>
+      <c r="AI46" s="61"/>
+      <c r="AJ46" s="61"/>
+      <c r="AK46" s="61"/>
+      <c r="AL46" s="61"/>
+      <c r="AM46" s="42"/>
+    </row>
+    <row r="47" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE47" s="55"/>
+      <c r="AF47" s="61"/>
+      <c r="AG47" s="61"/>
+      <c r="AH47" s="61"/>
+      <c r="AI47" s="61"/>
+      <c r="AJ47" s="61"/>
+      <c r="AK47" s="61"/>
+      <c r="AL47" s="61"/>
+      <c r="AM47" s="42"/>
+    </row>
+    <row r="48" spans="3:49" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE48" s="55"/>
+      <c r="AF48" s="61"/>
+      <c r="AG48" s="61"/>
+      <c r="AH48" s="61"/>
+      <c r="AI48" s="61"/>
+      <c r="AJ48" s="61"/>
+      <c r="AK48" s="61"/>
+      <c r="AL48" s="61"/>
+      <c r="AM48" s="42"/>
+    </row>
+    <row r="49" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE49" s="55"/>
+      <c r="AF49" s="61"/>
+      <c r="AG49" s="61"/>
+      <c r="AH49" s="61"/>
+      <c r="AI49" s="61"/>
+      <c r="AJ49" s="61"/>
+      <c r="AK49" s="61"/>
+      <c r="AL49" s="61"/>
+      <c r="AM49" s="42"/>
+    </row>
+    <row r="50" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE50" s="55"/>
+      <c r="AF50" s="61"/>
+      <c r="AG50" s="61"/>
+      <c r="AH50" s="61"/>
+      <c r="AI50" s="61"/>
+      <c r="AJ50" s="61"/>
+      <c r="AK50" s="61"/>
+      <c r="AL50" s="61"/>
+      <c r="AM50" s="42"/>
+    </row>
+    <row r="51" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE51" s="55"/>
+      <c r="AF51" s="61"/>
+      <c r="AG51" s="61"/>
+      <c r="AH51" s="61"/>
+      <c r="AI51" s="61"/>
+      <c r="AJ51" s="61"/>
+      <c r="AK51" s="61"/>
+      <c r="AL51" s="61"/>
+      <c r="AM51" s="42"/>
+    </row>
+    <row r="52" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE52" s="55"/>
+      <c r="AF52" s="61"/>
+      <c r="AG52" s="61"/>
+      <c r="AH52" s="61"/>
+      <c r="AI52" s="61"/>
+      <c r="AJ52" s="61"/>
+      <c r="AK52" s="110" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL52" s="111">
+        <f>W33</f>
+        <v>4029.9999999999982</v>
+      </c>
+      <c r="AM52" s="42"/>
+    </row>
+    <row r="53" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE53" s="55"/>
+      <c r="AF53" s="61"/>
+      <c r="AG53" s="61"/>
+      <c r="AH53" s="61"/>
+      <c r="AI53" s="61"/>
+      <c r="AJ53" s="61"/>
+      <c r="AK53" s="61"/>
+      <c r="AL53" s="61"/>
+      <c r="AM53" s="42"/>
+    </row>
+    <row r="54" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE54" s="55"/>
+      <c r="AF54" s="61"/>
+      <c r="AG54" s="61"/>
+      <c r="AH54" s="61"/>
+      <c r="AI54" s="61"/>
+      <c r="AJ54" s="61"/>
+      <c r="AK54" s="61"/>
+      <c r="AL54" s="61"/>
+      <c r="AM54" s="42"/>
+    </row>
+    <row r="55" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE55" s="55"/>
+      <c r="AF55" s="61"/>
+      <c r="AG55" s="61"/>
+      <c r="AH55" s="61"/>
+      <c r="AI55" s="61"/>
+      <c r="AJ55" s="61"/>
+      <c r="AK55" s="61"/>
+      <c r="AL55" s="61"/>
+      <c r="AM55" s="42"/>
+    </row>
+    <row r="56" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE56" s="55"/>
+      <c r="AF56" s="61"/>
+      <c r="AG56" s="61"/>
+      <c r="AH56" s="61"/>
+      <c r="AI56" s="61"/>
+      <c r="AJ56" s="61"/>
+      <c r="AK56" s="61"/>
+      <c r="AL56" s="61"/>
+      <c r="AM56" s="42"/>
+    </row>
+    <row r="57" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE57" s="55"/>
+      <c r="AF57" s="61"/>
+      <c r="AG57" s="61"/>
+      <c r="AH57" s="61"/>
+      <c r="AI57" s="61"/>
+      <c r="AJ57" s="61"/>
+      <c r="AK57" s="61"/>
+      <c r="AL57" s="61"/>
+      <c r="AM57" s="42"/>
+    </row>
+    <row r="58" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE58" s="55"/>
+      <c r="AF58" s="61"/>
+      <c r="AG58" s="61"/>
+      <c r="AH58" s="61"/>
+      <c r="AI58" s="61"/>
+      <c r="AJ58" s="61"/>
+      <c r="AK58" s="61"/>
+      <c r="AL58" s="61"/>
+      <c r="AM58" s="42"/>
+    </row>
+    <row r="59" spans="31:39" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE59" s="95"/>
+      <c r="AF59" s="96"/>
+      <c r="AG59" s="96"/>
+      <c r="AH59" s="96"/>
+      <c r="AI59" s="96"/>
+      <c r="AJ59" s="96"/>
+      <c r="AK59" s="96"/>
+      <c r="AL59" s="96"/>
+      <c r="AM59" s="99"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="AF8:AL8"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="C1:N3"/>
+    <mergeCell ref="L6:M7"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="D7:J15"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="D24:D29"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="D30:D35"/>
+    <mergeCell ref="AF34:AL34"/>
+    <mergeCell ref="AP16:AV16"/>
+    <mergeCell ref="AP30:AV30"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4453F609-292E-164E-A751-36DE4F18CCDD}">
   <dimension ref="C1:I21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.83203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8974,33 +15896,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:9" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="145" t="s">
+      <c r="C1" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
     </row>
     <row r="2" spans="3:9" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
     </row>
     <row r="3" spans="3:9" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="145"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="145"/>
-      <c r="H3" s="145"/>
-      <c r="I3" s="145"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
     </row>
     <row r="5" spans="3:9" s="11" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="4"/>
